--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3371" uniqueCount="2081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3374" uniqueCount="2083">
   <si>
     <t xml:space="preserve">db_name</t>
   </si>
@@ -2783,6 +2783,12 @@
   </si>
   <si>
     <t xml:space="preserve">kizimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karangetang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">karangetang</t>
   </si>
   <si>
     <t xml:space="preserve">Klabat</t>
@@ -6272,7 +6278,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -6299,6 +6305,11 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -6343,13 +6354,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6369,8 +6384,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1073"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F1074"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.67"/>
@@ -13012,12 +13027,12 @@
         <v>921</v>
       </c>
       <c r="B474" s="0" t="n">
-        <v>266120</v>
-      </c>
-      <c r="C474" s="0" t="s">
+        <v>267020</v>
+      </c>
+      <c r="C474" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="D474" s="0" t="s">
+      <c r="D474" s="2" t="s">
         <v>922</v>
       </c>
     </row>
@@ -13026,7 +13041,7 @@
         <v>923</v>
       </c>
       <c r="B475" s="0" t="n">
-        <v>300260</v>
+        <v>266120</v>
       </c>
       <c r="C475" s="0" t="s">
         <v>924</v>
@@ -13037,27 +13052,27 @@
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B476" s="0" t="s">
-        <v>4</v>
+        <v>925</v>
+      </c>
+      <c r="B476" s="0" t="n">
+        <v>300260</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>4</v>
+        <v>926</v>
       </c>
       <c r="D476" s="0" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="0" t="s">
-        <v>926</v>
-      </c>
-      <c r="B477" s="0" t="n">
-        <v>375010</v>
+        <v>4</v>
+      </c>
+      <c r="B477" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>927</v>
+        <v>4</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>927</v>
@@ -13068,7 +13083,7 @@
         <v>928</v>
       </c>
       <c r="B478" s="0" t="n">
-        <v>290120</v>
+        <v>375010</v>
       </c>
       <c r="C478" s="0" t="s">
         <v>929</v>
@@ -13082,7 +13097,7 @@
         <v>930</v>
       </c>
       <c r="B479" s="0" t="n">
-        <v>300220</v>
+        <v>290120</v>
       </c>
       <c r="C479" s="0" t="s">
         <v>931</v>
@@ -13096,7 +13111,7 @@
         <v>932</v>
       </c>
       <c r="B480" s="0" t="n">
-        <v>221200</v>
+        <v>300220</v>
       </c>
       <c r="C480" s="0" t="s">
         <v>933</v>
@@ -13110,7 +13125,7 @@
         <v>934</v>
       </c>
       <c r="B481" s="0" t="n">
-        <v>311140</v>
+        <v>221200</v>
       </c>
       <c r="C481" s="0" t="s">
         <v>935</v>
@@ -13121,27 +13136,27 @@
     </row>
     <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B482" s="0" t="s">
-        <v>4</v>
+        <v>936</v>
+      </c>
+      <c r="B482" s="0" t="n">
+        <v>311140</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>4</v>
+        <v>937</v>
       </c>
       <c r="D482" s="0" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="0" t="s">
-        <v>937</v>
-      </c>
-      <c r="B483" s="0" t="n">
-        <v>221320</v>
+        <v>4</v>
+      </c>
+      <c r="B483" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>938</v>
+        <v>4</v>
       </c>
       <c r="D483" s="0" t="s">
         <v>938</v>
@@ -13152,7 +13167,7 @@
         <v>939</v>
       </c>
       <c r="B484" s="0" t="n">
-        <v>222054</v>
+        <v>221320</v>
       </c>
       <c r="C484" s="0" t="s">
         <v>940</v>
@@ -13166,7 +13181,7 @@
         <v>941</v>
       </c>
       <c r="B485" s="0" t="n">
-        <v>311161</v>
+        <v>222054</v>
       </c>
       <c r="C485" s="0" t="s">
         <v>942</v>
@@ -13180,7 +13195,7 @@
         <v>943</v>
       </c>
       <c r="B486" s="0" t="n">
-        <v>300090</v>
+        <v>311161</v>
       </c>
       <c r="C486" s="0" t="s">
         <v>944</v>
@@ -13194,7 +13209,7 @@
         <v>945</v>
       </c>
       <c r="B487" s="0" t="n">
-        <v>300020</v>
+        <v>300090</v>
       </c>
       <c r="C487" s="0" t="s">
         <v>946</v>
@@ -13208,7 +13223,7 @@
         <v>947</v>
       </c>
       <c r="B488" s="0" t="n">
-        <v>300122</v>
+        <v>300020</v>
       </c>
       <c r="C488" s="0" t="s">
         <v>948</v>
@@ -13219,27 +13234,27 @@
     </row>
     <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B489" s="0" t="s">
-        <v>4</v>
+        <v>949</v>
+      </c>
+      <c r="B489" s="0" t="n">
+        <v>300122</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="D489" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="0" t="s">
-        <v>950</v>
-      </c>
-      <c r="B490" s="0" t="n">
-        <v>300330</v>
+        <v>4</v>
+      </c>
+      <c r="B490" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>951</v>
+        <v>4</v>
       </c>
       <c r="D490" s="0" t="s">
         <v>951</v>
@@ -13250,7 +13265,7 @@
         <v>952</v>
       </c>
       <c r="B491" s="0" t="n">
-        <v>373</v>
+        <v>300330</v>
       </c>
       <c r="C491" s="0" t="s">
         <v>953</v>
@@ -13264,7 +13279,7 @@
         <v>954</v>
       </c>
       <c r="B492" s="0" t="n">
-        <v>300400</v>
+        <v>373</v>
       </c>
       <c r="C492" s="0" t="s">
         <v>955</v>
@@ -13278,7 +13293,7 @@
         <v>956</v>
       </c>
       <c r="B493" s="0" t="n">
-        <v>262000</v>
+        <v>300400</v>
       </c>
       <c r="C493" s="0" t="s">
         <v>957</v>
@@ -13292,7 +13307,7 @@
         <v>958</v>
       </c>
       <c r="B494" s="0" t="n">
-        <v>300190</v>
+        <v>262000</v>
       </c>
       <c r="C494" s="0" t="s">
         <v>959</v>
@@ -13306,7 +13321,7 @@
         <v>960</v>
       </c>
       <c r="B495" s="0" t="n">
-        <v>300200</v>
+        <v>300190</v>
       </c>
       <c r="C495" s="0" t="s">
         <v>961</v>
@@ -13317,27 +13332,27 @@
     </row>
     <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B496" s="0" t="s">
-        <v>4</v>
+        <v>962</v>
+      </c>
+      <c r="B496" s="0" t="n">
+        <v>300200</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>4</v>
+        <v>963</v>
       </c>
       <c r="D496" s="0" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="0" t="s">
-        <v>963</v>
-      </c>
-      <c r="B497" s="0" t="n">
-        <v>371030</v>
+        <v>4</v>
+      </c>
+      <c r="B497" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>964</v>
+        <v>4</v>
       </c>
       <c r="D497" s="0" t="s">
         <v>964</v>
@@ -13348,7 +13363,7 @@
         <v>965</v>
       </c>
       <c r="B498" s="0" t="n">
-        <v>300050</v>
+        <v>371030</v>
       </c>
       <c r="C498" s="0" t="s">
         <v>966</v>
@@ -13359,16 +13374,16 @@
     </row>
     <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B499" s="0" t="s">
-        <v>4</v>
+        <v>967</v>
+      </c>
+      <c r="B499" s="0" t="n">
+        <v>300050</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>4</v>
+        <v>968</v>
       </c>
       <c r="D499" s="0" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13382,7 +13397,7 @@
         <v>4</v>
       </c>
       <c r="D500" s="0" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13396,7 +13411,7 @@
         <v>4</v>
       </c>
       <c r="D501" s="0" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13410,18 +13425,18 @@
         <v>4</v>
       </c>
       <c r="D502" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="0" t="s">
-        <v>971</v>
-      </c>
-      <c r="B503" s="0" t="n">
-        <v>312230</v>
+        <v>4</v>
+      </c>
+      <c r="B503" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C503" s="0" t="s">
-        <v>972</v>
+        <v>4</v>
       </c>
       <c r="D503" s="0" t="s">
         <v>972</v>
@@ -13432,7 +13447,7 @@
         <v>973</v>
       </c>
       <c r="B504" s="0" t="n">
-        <v>213000</v>
+        <v>312230</v>
       </c>
       <c r="C504" s="0" t="s">
         <v>974</v>
@@ -13446,7 +13461,7 @@
         <v>975</v>
       </c>
       <c r="B505" s="0" t="n">
-        <v>300370</v>
+        <v>213000</v>
       </c>
       <c r="C505" s="0" t="s">
         <v>976</v>
@@ -13460,7 +13475,7 @@
         <v>977</v>
       </c>
       <c r="B506" s="0" t="n">
-        <v>304030</v>
+        <v>300370</v>
       </c>
       <c r="C506" s="0" t="s">
         <v>978</v>
@@ -13471,27 +13486,27 @@
     </row>
     <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B507" s="0" t="s">
-        <v>4</v>
+        <v>979</v>
+      </c>
+      <c r="B507" s="0" t="n">
+        <v>304030</v>
       </c>
       <c r="C507" s="0" t="s">
-        <v>4</v>
+        <v>980</v>
       </c>
       <c r="D507" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="0" t="s">
-        <v>980</v>
-      </c>
-      <c r="B508" s="0" t="n">
-        <v>300023</v>
+        <v>4</v>
+      </c>
+      <c r="B508" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C508" s="0" t="s">
-        <v>981</v>
+        <v>4</v>
       </c>
       <c r="D508" s="0" t="s">
         <v>981</v>
@@ -13502,7 +13517,7 @@
         <v>982</v>
       </c>
       <c r="B509" s="0" t="n">
-        <v>221120</v>
+        <v>300023</v>
       </c>
       <c r="C509" s="0" t="s">
         <v>983</v>
@@ -13513,16 +13528,16 @@
     </row>
     <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B510" s="0" t="s">
-        <v>4</v>
+        <v>984</v>
+      </c>
+      <c r="B510" s="0" t="n">
+        <v>221120</v>
       </c>
       <c r="C510" s="0" t="s">
-        <v>4</v>
+        <v>985</v>
       </c>
       <c r="D510" s="0" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13536,7 +13551,7 @@
         <v>4</v>
       </c>
       <c r="D511" s="0" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13550,18 +13565,18 @@
         <v>4</v>
       </c>
       <c r="D512" s="0" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="0" t="s">
-        <v>987</v>
-      </c>
-      <c r="B513" s="0" t="n">
-        <v>225040</v>
+        <v>4</v>
+      </c>
+      <c r="B513" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C513" s="0" t="s">
-        <v>988</v>
+        <v>4</v>
       </c>
       <c r="D513" s="0" t="s">
         <v>988</v>
@@ -13572,7 +13587,7 @@
         <v>989</v>
       </c>
       <c r="B514" s="0" t="n">
-        <v>373050</v>
+        <v>225040</v>
       </c>
       <c r="C514" s="0" t="s">
         <v>990</v>
@@ -13586,7 +13601,7 @@
         <v>991</v>
       </c>
       <c r="B515" s="0" t="n">
-        <v>223002</v>
+        <v>373050</v>
       </c>
       <c r="C515" s="0" t="s">
         <v>992</v>
@@ -13600,7 +13615,7 @@
         <v>993</v>
       </c>
       <c r="B516" s="0" t="n">
-        <v>222170</v>
+        <v>223002</v>
       </c>
       <c r="C516" s="0" t="s">
         <v>994</v>
@@ -13611,16 +13626,16 @@
     </row>
     <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B517" s="0" t="s">
-        <v>4</v>
+        <v>995</v>
+      </c>
+      <c r="B517" s="0" t="n">
+        <v>222170</v>
       </c>
       <c r="C517" s="0" t="s">
-        <v>4</v>
+        <v>996</v>
       </c>
       <c r="D517" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13634,18 +13649,18 @@
         <v>4</v>
       </c>
       <c r="D518" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="0" t="s">
-        <v>997</v>
-      </c>
-      <c r="B519" s="0" t="n">
-        <v>343101</v>
+        <v>4</v>
+      </c>
+      <c r="B519" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C519" s="0" t="s">
-        <v>998</v>
+        <v>4</v>
       </c>
       <c r="D519" s="0" t="s">
         <v>998</v>
@@ -13656,7 +13671,7 @@
         <v>999</v>
       </c>
       <c r="B520" s="0" t="n">
-        <v>357102</v>
+        <v>343101</v>
       </c>
       <c r="C520" s="0" t="s">
         <v>1000</v>
@@ -13670,7 +13685,7 @@
         <v>1001</v>
       </c>
       <c r="B521" s="0" t="n">
-        <v>273080</v>
+        <v>357102</v>
       </c>
       <c r="C521" s="0" t="s">
         <v>1002</v>
@@ -13684,7 +13699,7 @@
         <v>1003</v>
       </c>
       <c r="B522" s="0" t="n">
-        <v>357061</v>
+        <v>273080</v>
       </c>
       <c r="C522" s="0" t="s">
         <v>1004</v>
@@ -13698,7 +13713,7 @@
         <v>1005</v>
       </c>
       <c r="B523" s="0" t="n">
-        <v>355035</v>
+        <v>357061</v>
       </c>
       <c r="C523" s="0" t="s">
         <v>1006</v>
@@ -13712,24 +13727,24 @@
         <v>1007</v>
       </c>
       <c r="B524" s="0" t="n">
-        <v>357092</v>
+        <v>355035</v>
       </c>
       <c r="C524" s="0" t="s">
         <v>1008</v>
       </c>
       <c r="D524" s="0" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="0" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B525" s="0" t="n">
+        <v>357092</v>
+      </c>
+      <c r="C525" s="0" t="s">
         <v>1010</v>
-      </c>
-      <c r="B525" s="0" t="n">
-        <v>343150</v>
-      </c>
-      <c r="C525" s="0" t="s">
-        <v>1011</v>
       </c>
       <c r="D525" s="0" t="s">
         <v>1011</v>
@@ -13740,7 +13755,7 @@
         <v>1012</v>
       </c>
       <c r="B526" s="0" t="n">
-        <v>321091</v>
+        <v>343150</v>
       </c>
       <c r="C526" s="0" t="s">
         <v>1013</v>
@@ -13751,27 +13766,27 @@
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B527" s="0" t="s">
-        <v>4</v>
+        <v>1014</v>
+      </c>
+      <c r="B527" s="0" t="n">
+        <v>321091</v>
       </c>
       <c r="C527" s="0" t="s">
-        <v>4</v>
+        <v>1015</v>
       </c>
       <c r="D527" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="0" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B528" s="0" t="n">
-        <v>263320</v>
+        <v>4</v>
+      </c>
+      <c r="B528" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C528" s="0" t="s">
-        <v>1016</v>
+        <v>4</v>
       </c>
       <c r="D528" s="0" t="s">
         <v>1016</v>
@@ -13782,7 +13797,7 @@
         <v>1017</v>
       </c>
       <c r="B529" s="0" t="n">
-        <v>355108</v>
+        <v>263320</v>
       </c>
       <c r="C529" s="0" t="s">
         <v>1018</v>
@@ -13793,27 +13808,27 @@
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B530" s="0" t="s">
-        <v>4</v>
+        <v>1019</v>
+      </c>
+      <c r="B530" s="0" t="n">
+        <v>355108</v>
       </c>
       <c r="C530" s="0" t="s">
-        <v>4</v>
+        <v>1020</v>
       </c>
       <c r="D530" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="0" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B531" s="0" t="n">
-        <v>311080</v>
+        <v>4</v>
+      </c>
+      <c r="B531" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C531" s="0" t="s">
-        <v>1021</v>
+        <v>4</v>
       </c>
       <c r="D531" s="0" t="s">
         <v>1021</v>
@@ -13821,27 +13836,27 @@
     </row>
     <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B532" s="0" t="s">
-        <v>4</v>
+        <v>1022</v>
+      </c>
+      <c r="B532" s="0" t="n">
+        <v>311080</v>
       </c>
       <c r="C532" s="0" t="s">
-        <v>4</v>
+        <v>1023</v>
       </c>
       <c r="D532" s="0" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="0" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B533" s="0" t="n">
-        <v>383060</v>
+        <v>4</v>
+      </c>
+      <c r="B533" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C533" s="0" t="s">
-        <v>1024</v>
+        <v>4</v>
       </c>
       <c r="D533" s="0" t="s">
         <v>1024</v>
@@ -13852,7 +13867,7 @@
         <v>1025</v>
       </c>
       <c r="B534" s="0" t="n">
-        <v>211001</v>
+        <v>383060</v>
       </c>
       <c r="C534" s="0" t="s">
         <v>1026</v>
@@ -13866,7 +13881,7 @@
         <v>1027</v>
       </c>
       <c r="B535" s="0" t="n">
-        <v>355100</v>
+        <v>211001</v>
       </c>
       <c r="C535" s="0" t="s">
         <v>1028</v>
@@ -13880,7 +13895,7 @@
         <v>1029</v>
       </c>
       <c r="B536" s="0" t="n">
-        <v>341098</v>
+        <v>355100</v>
       </c>
       <c r="C536" s="0" t="s">
         <v>1030</v>
@@ -13894,7 +13909,7 @@
         <v>1031</v>
       </c>
       <c r="B537" s="0" t="n">
-        <v>383010</v>
+        <v>341098</v>
       </c>
       <c r="C537" s="0" t="s">
         <v>1032</v>
@@ -13908,7 +13923,7 @@
         <v>1033</v>
       </c>
       <c r="B538" s="0" t="n">
-        <v>344133</v>
+        <v>383010</v>
       </c>
       <c r="C538" s="0" t="s">
         <v>1034</v>
@@ -13922,7 +13937,7 @@
         <v>1035</v>
       </c>
       <c r="B539" s="0" t="n">
-        <v>344080</v>
+        <v>344133</v>
       </c>
       <c r="C539" s="0" t="s">
         <v>1036</v>
@@ -13936,7 +13951,7 @@
         <v>1037</v>
       </c>
       <c r="B540" s="0" t="n">
-        <v>323080</v>
+        <v>344080</v>
       </c>
       <c r="C540" s="0" t="s">
         <v>1038</v>
@@ -13950,7 +13965,7 @@
         <v>1039</v>
       </c>
       <c r="B541" s="0" t="n">
-        <v>355120</v>
+        <v>323080</v>
       </c>
       <c r="C541" s="0" t="s">
         <v>1040</v>
@@ -13964,7 +13979,7 @@
         <v>1041</v>
       </c>
       <c r="B542" s="0" t="n">
-        <v>271050</v>
+        <v>355120</v>
       </c>
       <c r="C542" s="0" t="s">
         <v>1042</v>
@@ -13978,7 +13993,7 @@
         <v>1043</v>
       </c>
       <c r="B543" s="0" t="n">
-        <v>358060</v>
+        <v>271050</v>
       </c>
       <c r="C543" s="0" t="s">
         <v>1044</v>
@@ -13992,7 +14007,7 @@
         <v>1045</v>
       </c>
       <c r="B544" s="0" t="n">
-        <v>323190</v>
+        <v>358060</v>
       </c>
       <c r="C544" s="0" t="s">
         <v>1046</v>
@@ -14006,7 +14021,7 @@
         <v>1047</v>
       </c>
       <c r="B545" s="0" t="n">
-        <v>263260</v>
+        <v>323190</v>
       </c>
       <c r="C545" s="0" t="s">
         <v>1048</v>
@@ -14020,7 +14035,7 @@
         <v>1049</v>
       </c>
       <c r="B546" s="0" t="n">
-        <v>271031</v>
+        <v>263260</v>
       </c>
       <c r="C546" s="0" t="s">
         <v>1050</v>
@@ -14034,7 +14049,7 @@
         <v>1051</v>
       </c>
       <c r="B547" s="0" t="n">
-        <v>264200</v>
+        <v>271031</v>
       </c>
       <c r="C547" s="0" t="s">
         <v>1052</v>
@@ -14048,7 +14063,7 @@
         <v>1053</v>
       </c>
       <c r="B548" s="0" t="n">
-        <v>300530</v>
+        <v>264200</v>
       </c>
       <c r="C548" s="0" t="s">
         <v>1054</v>
@@ -14062,7 +14077,7 @@
         <v>1055</v>
       </c>
       <c r="B549" s="0" t="n">
-        <v>320050</v>
+        <v>300530</v>
       </c>
       <c r="C549" s="0" t="s">
         <v>1056</v>
@@ -14076,7 +14091,7 @@
         <v>1057</v>
       </c>
       <c r="B550" s="0" t="n">
-        <v>264180</v>
+        <v>320050</v>
       </c>
       <c r="C550" s="0" t="s">
         <v>1058</v>
@@ -14090,7 +14105,7 @@
         <v>1059</v>
       </c>
       <c r="B551" s="0" t="n">
-        <v>264230</v>
+        <v>264180</v>
       </c>
       <c r="C551" s="0" t="s">
         <v>1060</v>
@@ -14101,27 +14116,27 @@
     </row>
     <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B552" s="0" t="s">
-        <v>4</v>
+        <v>1061</v>
+      </c>
+      <c r="B552" s="0" t="n">
+        <v>264230</v>
       </c>
       <c r="C552" s="0" t="s">
-        <v>4</v>
+        <v>1062</v>
       </c>
       <c r="D552" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="0" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B553" s="0" t="n">
-        <v>360030</v>
+        <v>4</v>
+      </c>
+      <c r="B553" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C553" s="0" t="s">
-        <v>1063</v>
+        <v>4</v>
       </c>
       <c r="D553" s="0" t="s">
         <v>1063</v>
@@ -14132,7 +14147,7 @@
         <v>1064</v>
       </c>
       <c r="B554" s="0" t="n">
-        <v>355092</v>
+        <v>360030</v>
       </c>
       <c r="C554" s="0" t="s">
         <v>1065</v>
@@ -14143,27 +14158,27 @@
     </row>
     <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B555" s="0" t="s">
-        <v>4</v>
+        <v>1066</v>
+      </c>
+      <c r="B555" s="0" t="n">
+        <v>355092</v>
       </c>
       <c r="C555" s="0" t="s">
-        <v>4</v>
+        <v>1067</v>
       </c>
       <c r="D555" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="0" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B556" s="0" t="n">
-        <v>211042</v>
+        <v>4</v>
+      </c>
+      <c r="B556" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C556" s="0" t="s">
-        <v>1068</v>
+        <v>4</v>
       </c>
       <c r="D556" s="0" t="s">
         <v>1068</v>
@@ -14174,7 +14189,7 @@
         <v>1069</v>
       </c>
       <c r="B557" s="0" t="n">
-        <v>370030</v>
+        <v>211042</v>
       </c>
       <c r="C557" s="0" t="s">
         <v>1070</v>
@@ -14188,7 +14203,7 @@
         <v>1071</v>
       </c>
       <c r="B558" s="0" t="n">
-        <v>357110</v>
+        <v>370030</v>
       </c>
       <c r="C558" s="0" t="s">
         <v>1072</v>
@@ -14202,7 +14217,7 @@
         <v>1073</v>
       </c>
       <c r="B559" s="0" t="n">
-        <v>355110</v>
+        <v>357110</v>
       </c>
       <c r="C559" s="0" t="s">
         <v>1074</v>
@@ -14216,7 +14231,7 @@
         <v>1075</v>
       </c>
       <c r="B560" s="0" t="n">
-        <v>266100</v>
+        <v>355110</v>
       </c>
       <c r="C560" s="0" t="s">
         <v>1076</v>
@@ -14227,16 +14242,16 @@
     </row>
     <row r="561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B561" s="0" t="s">
-        <v>4</v>
+        <v>1077</v>
+      </c>
+      <c r="B561" s="0" t="n">
+        <v>266100</v>
       </c>
       <c r="C561" s="0" t="s">
-        <v>4</v>
+        <v>1078</v>
       </c>
       <c r="D561" s="0" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14250,18 +14265,18 @@
         <v>4</v>
       </c>
       <c r="D562" s="0" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="0" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B563" s="0" t="n">
-        <v>357064</v>
+        <v>4</v>
+      </c>
+      <c r="B563" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C563" s="0" t="s">
-        <v>1080</v>
+        <v>4</v>
       </c>
       <c r="D563" s="0" t="s">
         <v>1080</v>
@@ -14272,7 +14287,7 @@
         <v>1081</v>
       </c>
       <c r="B564" s="0" t="n">
-        <v>305050</v>
+        <v>357064</v>
       </c>
       <c r="C564" s="0" t="s">
         <v>1082</v>
@@ -14283,27 +14298,27 @@
     </row>
     <row r="565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B565" s="0" t="s">
-        <v>4</v>
+        <v>1083</v>
+      </c>
+      <c r="B565" s="0" t="n">
+        <v>305050</v>
       </c>
       <c r="C565" s="0" t="s">
-        <v>4</v>
+        <v>1084</v>
       </c>
       <c r="D565" s="0" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="0" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B566" s="0" t="n">
-        <v>222100</v>
+        <v>4</v>
+      </c>
+      <c r="B566" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C566" s="0" t="s">
-        <v>1085</v>
+        <v>4</v>
       </c>
       <c r="D566" s="0" t="s">
         <v>1085</v>
@@ -14314,7 +14329,7 @@
         <v>1086</v>
       </c>
       <c r="B567" s="0" t="n">
-        <v>357100</v>
+        <v>222100</v>
       </c>
       <c r="C567" s="0" t="s">
         <v>1087</v>
@@ -14328,7 +14343,7 @@
         <v>1088</v>
       </c>
       <c r="B568" s="0" t="n">
-        <v>341094</v>
+        <v>357100</v>
       </c>
       <c r="C568" s="0" t="s">
         <v>1089</v>
@@ -14342,7 +14357,7 @@
         <v>1090</v>
       </c>
       <c r="B569" s="0" t="n">
-        <v>341093</v>
+        <v>341094</v>
       </c>
       <c r="C569" s="0" t="s">
         <v>1091</v>
@@ -14356,7 +14371,7 @@
         <v>1092</v>
       </c>
       <c r="B570" s="0" t="n">
-        <v>261111</v>
+        <v>341093</v>
       </c>
       <c r="C570" s="0" t="s">
         <v>1093</v>
@@ -14370,7 +14385,7 @@
         <v>1094</v>
       </c>
       <c r="B571" s="0" t="n">
-        <v>221111</v>
+        <v>261111</v>
       </c>
       <c r="C571" s="0" t="s">
         <v>1095</v>
@@ -14384,38 +14399,38 @@
         <v>1096</v>
       </c>
       <c r="B572" s="0" t="n">
-        <v>358056</v>
+        <v>221111</v>
       </c>
       <c r="C572" s="0" t="s">
         <v>1097</v>
       </c>
       <c r="D572" s="0" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="0" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B573" s="0" t="n">
+        <v>358056</v>
+      </c>
+      <c r="C573" s="0" t="s">
         <v>1099</v>
       </c>
-      <c r="B573" s="0" t="n">
-        <v>351040</v>
-      </c>
-      <c r="C573" s="0" t="s">
+      <c r="D573" s="0" t="s">
         <v>1100</v>
-      </c>
-      <c r="D573" s="0" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="0" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B574" s="0" t="n">
+        <v>351040</v>
+      </c>
+      <c r="C574" s="0" t="s">
         <v>1102</v>
-      </c>
-      <c r="B574" s="0" t="n">
-        <v>312150</v>
-      </c>
-      <c r="C574" s="0" t="s">
-        <v>1103</v>
       </c>
       <c r="D574" s="0" t="s">
         <v>1103</v>
@@ -14426,7 +14441,7 @@
         <v>1104</v>
       </c>
       <c r="B575" s="0" t="n">
-        <v>272070</v>
+        <v>312150</v>
       </c>
       <c r="C575" s="0" t="s">
         <v>1105</v>
@@ -14440,7 +14455,7 @@
         <v>1106</v>
       </c>
       <c r="B576" s="0" t="n">
-        <v>266110</v>
+        <v>272070</v>
       </c>
       <c r="C576" s="0" t="s">
         <v>1107</v>
@@ -14454,7 +14469,7 @@
         <v>1108</v>
       </c>
       <c r="B577" s="0" t="n">
-        <v>357021</v>
+        <v>266110</v>
       </c>
       <c r="C577" s="0" t="s">
         <v>1109</v>
@@ -14468,7 +14483,7 @@
         <v>1110</v>
       </c>
       <c r="B578" s="0" t="n">
-        <v>271040</v>
+        <v>357021</v>
       </c>
       <c r="C578" s="0" t="s">
         <v>1111</v>
@@ -14482,7 +14497,7 @@
         <v>1112</v>
       </c>
       <c r="B579" s="0" t="n">
-        <v>268070</v>
+        <v>271040</v>
       </c>
       <c r="C579" s="0" t="s">
         <v>1113</v>
@@ -14496,7 +14511,7 @@
         <v>1114</v>
       </c>
       <c r="B580" s="0" t="n">
-        <v>311310</v>
+        <v>268070</v>
       </c>
       <c r="C580" s="0" t="s">
         <v>1115</v>
@@ -14507,27 +14522,27 @@
     </row>
     <row r="581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B581" s="0" t="s">
-        <v>4</v>
+        <v>1116</v>
+      </c>
+      <c r="B581" s="0" t="n">
+        <v>311310</v>
       </c>
       <c r="C581" s="0" t="s">
-        <v>4</v>
+        <v>1117</v>
       </c>
       <c r="D581" s="0" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="0" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B582" s="0" t="n">
-        <v>271071</v>
+        <v>4</v>
+      </c>
+      <c r="B582" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C582" s="0" t="s">
-        <v>1118</v>
+        <v>4</v>
       </c>
       <c r="D582" s="0" t="s">
         <v>1118</v>
@@ -14538,7 +14553,7 @@
         <v>1119</v>
       </c>
       <c r="B583" s="0" t="n">
-        <v>273044</v>
+        <v>271071</v>
       </c>
       <c r="C583" s="0" t="s">
         <v>1120</v>
@@ -14552,7 +14567,7 @@
         <v>1121</v>
       </c>
       <c r="B584" s="0" t="n">
-        <v>261121</v>
+        <v>273044</v>
       </c>
       <c r="C584" s="0" t="s">
         <v>1122</v>
@@ -14563,27 +14578,27 @@
     </row>
     <row r="585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B585" s="0" t="s">
-        <v>4</v>
+        <v>1123</v>
+      </c>
+      <c r="B585" s="0" t="n">
+        <v>261121</v>
       </c>
       <c r="C585" s="0" t="s">
-        <v>4</v>
+        <v>1124</v>
       </c>
       <c r="D585" s="0" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="0" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B586" s="0" t="n">
-        <v>300290</v>
+        <v>4</v>
+      </c>
+      <c r="B586" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C586" s="0" t="s">
-        <v>1125</v>
+        <v>4</v>
       </c>
       <c r="D586" s="0" t="s">
         <v>1125</v>
@@ -14594,7 +14609,7 @@
         <v>1126</v>
       </c>
       <c r="B587" s="0" t="n">
-        <v>300140</v>
+        <v>300290</v>
       </c>
       <c r="C587" s="0" t="s">
         <v>1127</v>
@@ -14608,7 +14623,7 @@
         <v>1128</v>
       </c>
       <c r="B588" s="0" t="n">
-        <v>323150</v>
+        <v>300140</v>
       </c>
       <c r="C588" s="0" t="s">
         <v>1129</v>
@@ -14619,27 +14634,27 @@
     </row>
     <row r="589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B589" s="0" t="s">
-        <v>4</v>
+        <v>1130</v>
+      </c>
+      <c r="B589" s="0" t="n">
+        <v>323150</v>
       </c>
       <c r="C589" s="0" t="s">
-        <v>4</v>
+        <v>1131</v>
       </c>
       <c r="D589" s="0" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="0" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B590" s="0" t="n">
-        <v>221127</v>
+        <v>4</v>
+      </c>
+      <c r="B590" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C590" s="0" t="s">
-        <v>1132</v>
+        <v>4</v>
       </c>
       <c r="D590" s="0" t="s">
         <v>1132</v>
@@ -14650,7 +14665,7 @@
         <v>1133</v>
       </c>
       <c r="B591" s="0" t="n">
-        <v>221115</v>
+        <v>221127</v>
       </c>
       <c r="C591" s="0" t="s">
         <v>1134</v>
@@ -14664,7 +14679,7 @@
         <v>1135</v>
       </c>
       <c r="B592" s="0" t="n">
-        <v>221122</v>
+        <v>221115</v>
       </c>
       <c r="C592" s="0" t="s">
         <v>1136</v>
@@ -14678,7 +14693,7 @@
         <v>1137</v>
       </c>
       <c r="B593" s="0" t="n">
-        <v>272030</v>
+        <v>221122</v>
       </c>
       <c r="C593" s="0" t="s">
         <v>1138</v>
@@ -14692,7 +14707,7 @@
         <v>1139</v>
       </c>
       <c r="B594" s="0" t="n">
-        <v>261140</v>
+        <v>272030</v>
       </c>
       <c r="C594" s="0" t="s">
         <v>1140</v>
@@ -14703,27 +14718,27 @@
     </row>
     <row r="595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B595" s="0" t="s">
-        <v>4</v>
+        <v>1141</v>
+      </c>
+      <c r="B595" s="0" t="n">
+        <v>261140</v>
       </c>
       <c r="C595" s="0" t="s">
-        <v>4</v>
+        <v>1142</v>
       </c>
       <c r="D595" s="0" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="0" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B596" s="0" t="n">
-        <v>268062</v>
+        <v>4</v>
+      </c>
+      <c r="B596" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C596" s="0" t="s">
-        <v>1143</v>
+        <v>4</v>
       </c>
       <c r="D596" s="0" t="s">
         <v>1143</v>
@@ -14734,7 +14749,7 @@
         <v>1144</v>
       </c>
       <c r="B597" s="0" t="n">
-        <v>273081</v>
+        <v>268062</v>
       </c>
       <c r="C597" s="0" t="s">
         <v>1145</v>
@@ -14748,7 +14763,7 @@
         <v>1146</v>
       </c>
       <c r="B598" s="0" t="n">
-        <v>327040</v>
+        <v>273081</v>
       </c>
       <c r="C598" s="0" t="s">
         <v>1147</v>
@@ -14762,7 +14777,7 @@
         <v>1148</v>
       </c>
       <c r="B599" s="0" t="n">
-        <v>241061</v>
+        <v>327040</v>
       </c>
       <c r="C599" s="0" t="s">
         <v>1149</v>
@@ -14776,7 +14791,7 @@
         <v>1150</v>
       </c>
       <c r="B600" s="0" t="n">
-        <v>222021</v>
+        <v>241061</v>
       </c>
       <c r="C600" s="0" t="s">
         <v>1151</v>
@@ -14790,7 +14805,7 @@
         <v>1152</v>
       </c>
       <c r="B601" s="0" t="n">
-        <v>313140</v>
+        <v>222021</v>
       </c>
       <c r="C601" s="0" t="s">
         <v>1153</v>
@@ -14801,27 +14816,27 @@
     </row>
     <row r="602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B602" s="0" t="s">
-        <v>4</v>
+        <v>1154</v>
+      </c>
+      <c r="B602" s="0" t="n">
+        <v>313140</v>
       </c>
       <c r="C602" s="0" t="s">
-        <v>4</v>
+        <v>1155</v>
       </c>
       <c r="D602" s="0" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A603" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="B603" s="0" t="n">
-        <v>273031</v>
+        <v>4</v>
+      </c>
+      <c r="B603" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C603" s="0" t="s">
-        <v>1156</v>
+        <v>4</v>
       </c>
       <c r="D603" s="0" t="s">
         <v>1156</v>
@@ -14832,7 +14847,7 @@
         <v>1157</v>
       </c>
       <c r="B604" s="0" t="n">
-        <v>344100</v>
+        <v>273031</v>
       </c>
       <c r="C604" s="0" t="s">
         <v>1158</v>
@@ -14846,7 +14861,7 @@
         <v>1159</v>
       </c>
       <c r="B605" s="0" t="n">
-        <v>341031</v>
+        <v>344100</v>
       </c>
       <c r="C605" s="0" t="s">
         <v>1160</v>
@@ -14860,7 +14875,7 @@
         <v>1161</v>
       </c>
       <c r="B606" s="0" t="n">
-        <v>300001</v>
+        <v>341031</v>
       </c>
       <c r="C606" s="0" t="s">
         <v>1162</v>
@@ -14871,27 +14886,27 @@
     </row>
     <row r="607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B607" s="0" t="s">
-        <v>4</v>
+        <v>1163</v>
+      </c>
+      <c r="B607" s="0" t="n">
+        <v>300001</v>
       </c>
       <c r="C607" s="0" t="s">
-        <v>4</v>
+        <v>1164</v>
       </c>
       <c r="D607" s="0" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A608" s="0" t="s">
-        <v>1164</v>
-      </c>
-      <c r="B608" s="0" t="n">
-        <v>221105</v>
+        <v>4</v>
+      </c>
+      <c r="B608" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C608" s="0" t="s">
-        <v>1165</v>
+        <v>4</v>
       </c>
       <c r="D608" s="0" t="s">
         <v>1165</v>
@@ -14902,7 +14917,7 @@
         <v>1166</v>
       </c>
       <c r="B609" s="0" t="n">
-        <v>271020</v>
+        <v>221105</v>
       </c>
       <c r="C609" s="0" t="s">
         <v>1167</v>
@@ -14916,7 +14931,7 @@
         <v>1168</v>
       </c>
       <c r="B610" s="0" t="n">
-        <v>332030</v>
+        <v>271020</v>
       </c>
       <c r="C610" s="0" t="s">
         <v>1169</v>
@@ -14930,7 +14945,7 @@
         <v>1170</v>
       </c>
       <c r="B611" s="0" t="n">
-        <v>332020</v>
+        <v>332030</v>
       </c>
       <c r="C611" s="0" t="s">
         <v>1171</v>
@@ -14944,7 +14959,7 @@
         <v>1172</v>
       </c>
       <c r="B612" s="0" t="n">
-        <v>273030</v>
+        <v>332020</v>
       </c>
       <c r="C612" s="0" t="s">
         <v>1173</v>
@@ -14958,7 +14973,7 @@
         <v>1174</v>
       </c>
       <c r="B613" s="0" t="n">
-        <v>241021</v>
+        <v>273030</v>
       </c>
       <c r="C613" s="0" t="s">
         <v>1175</v>
@@ -14972,7 +14987,7 @@
         <v>1176</v>
       </c>
       <c r="B614" s="0" t="n">
-        <v>320180</v>
+        <v>241021</v>
       </c>
       <c r="C614" s="0" t="s">
         <v>1177</v>
@@ -14986,7 +15001,7 @@
         <v>1178</v>
       </c>
       <c r="B615" s="0" t="n">
-        <v>323020</v>
+        <v>320180</v>
       </c>
       <c r="C615" s="0" t="s">
         <v>1179</v>
@@ -15000,7 +15015,7 @@
         <v>1180</v>
       </c>
       <c r="B616" s="0" t="n">
-        <v>221330</v>
+        <v>323020</v>
       </c>
       <c r="C616" s="0" t="s">
         <v>1181</v>
@@ -15011,27 +15026,27 @@
     </row>
     <row r="617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A617" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B617" s="0" t="s">
-        <v>4</v>
+        <v>1182</v>
+      </c>
+      <c r="B617" s="0" t="n">
+        <v>221330</v>
       </c>
       <c r="C617" s="0" t="s">
-        <v>4</v>
+        <v>1183</v>
       </c>
       <c r="D617" s="0" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="0" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B618" s="0" t="n">
-        <v>225050</v>
+        <v>4</v>
+      </c>
+      <c r="B618" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C618" s="0" t="s">
-        <v>1184</v>
+        <v>4</v>
       </c>
       <c r="D618" s="0" t="s">
         <v>1184</v>
@@ -15042,7 +15057,7 @@
         <v>1185</v>
       </c>
       <c r="B619" s="0" t="n">
-        <v>358052</v>
+        <v>225050</v>
       </c>
       <c r="C619" s="0" t="s">
         <v>1186</v>
@@ -15056,7 +15071,7 @@
         <v>1187</v>
       </c>
       <c r="B620" s="0" t="n">
-        <v>222060</v>
+        <v>358052</v>
       </c>
       <c r="C620" s="0" t="s">
         <v>1188</v>
@@ -15070,7 +15085,7 @@
         <v>1189</v>
       </c>
       <c r="B621" s="0" t="n">
-        <v>358054</v>
+        <v>222060</v>
       </c>
       <c r="C621" s="0" t="s">
         <v>1190</v>
@@ -15084,7 +15099,7 @@
         <v>1191</v>
       </c>
       <c r="B622" s="0" t="n">
-        <v>263250</v>
+        <v>358054</v>
       </c>
       <c r="C622" s="0" t="s">
         <v>1192</v>
@@ -15098,7 +15113,7 @@
         <v>1193</v>
       </c>
       <c r="B623" s="0" t="n">
-        <v>263240</v>
+        <v>263250</v>
       </c>
       <c r="C623" s="0" t="s">
         <v>1194</v>
@@ -15112,7 +15127,7 @@
         <v>1195</v>
       </c>
       <c r="B624" s="0" t="n">
-        <v>222160</v>
+        <v>263240</v>
       </c>
       <c r="C624" s="0" t="s">
         <v>1196</v>
@@ -15126,7 +15141,7 @@
         <v>1197</v>
       </c>
       <c r="B625" s="0" t="n">
-        <v>212020</v>
+        <v>222160</v>
       </c>
       <c r="C625" s="0" t="s">
         <v>1198</v>
@@ -15140,24 +15155,24 @@
         <v>1199</v>
       </c>
       <c r="B626" s="0" t="n">
-        <v>358064</v>
+        <v>212020</v>
       </c>
       <c r="C626" s="0" t="s">
         <v>1200</v>
       </c>
       <c r="D626" s="0" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="0" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B627" s="0" t="n">
+        <v>358064</v>
+      </c>
+      <c r="C627" s="0" t="s">
         <v>1202</v>
-      </c>
-      <c r="B627" s="0" t="n">
-        <v>300570</v>
-      </c>
-      <c r="C627" s="0" t="s">
-        <v>1203</v>
       </c>
       <c r="D627" s="0" t="s">
         <v>1203</v>
@@ -15168,7 +15183,7 @@
         <v>1204</v>
       </c>
       <c r="B628" s="0" t="n">
-        <v>358040</v>
+        <v>300570</v>
       </c>
       <c r="C628" s="0" t="s">
         <v>1205</v>
@@ -15182,38 +15197,38 @@
         <v>1206</v>
       </c>
       <c r="B629" s="0" t="n">
-        <v>341060</v>
+        <v>358040</v>
       </c>
       <c r="C629" s="0" t="s">
         <v>1207</v>
       </c>
       <c r="D629" s="0" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B630" s="0" t="s">
-        <v>4</v>
+        <v>1208</v>
+      </c>
+      <c r="B630" s="0" t="n">
+        <v>341060</v>
       </c>
       <c r="C630" s="0" t="s">
-        <v>4</v>
+        <v>1209</v>
       </c>
       <c r="D630" s="0" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="0" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B631" s="0" t="n">
-        <v>303050</v>
+        <v>4</v>
+      </c>
+      <c r="B631" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C631" s="0" t="s">
-        <v>1211</v>
+        <v>4</v>
       </c>
       <c r="D631" s="0" t="s">
         <v>1211</v>
@@ -15221,27 +15236,27 @@
     </row>
     <row r="632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B632" s="0" t="s">
-        <v>4</v>
+        <v>1212</v>
+      </c>
+      <c r="B632" s="0" t="n">
+        <v>303050</v>
       </c>
       <c r="C632" s="0" t="s">
-        <v>4</v>
+        <v>1213</v>
       </c>
       <c r="D632" s="0" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A633" s="0" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B633" s="0" t="n">
-        <v>320120</v>
+        <v>4</v>
+      </c>
+      <c r="B633" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C633" s="0" t="s">
-        <v>1214</v>
+        <v>4</v>
       </c>
       <c r="D633" s="0" t="s">
         <v>1214</v>
@@ -15252,7 +15267,7 @@
         <v>1215</v>
       </c>
       <c r="B634" s="0" t="n">
-        <v>290161</v>
+        <v>320120</v>
       </c>
       <c r="C634" s="0" t="s">
         <v>1216</v>
@@ -15266,7 +15281,7 @@
         <v>1217</v>
       </c>
       <c r="B635" s="0" t="n">
-        <v>212030</v>
+        <v>290161</v>
       </c>
       <c r="C635" s="0" t="s">
         <v>1218</v>
@@ -15280,24 +15295,24 @@
         <v>1219</v>
       </c>
       <c r="B636" s="0" t="n">
-        <v>355102</v>
+        <v>212030</v>
       </c>
       <c r="C636" s="0" t="s">
         <v>1220</v>
       </c>
       <c r="D636" s="0" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A637" s="0" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B637" s="0" t="n">
+        <v>355102</v>
+      </c>
+      <c r="C637" s="0" t="s">
         <v>1222</v>
-      </c>
-      <c r="B637" s="0" t="n">
-        <v>345030</v>
-      </c>
-      <c r="C637" s="0" t="s">
-        <v>1223</v>
       </c>
       <c r="D637" s="0" t="s">
         <v>1223</v>
@@ -15305,27 +15320,27 @@
     </row>
     <row r="638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A638" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B638" s="0" t="s">
-        <v>4</v>
+        <v>1224</v>
+      </c>
+      <c r="B638" s="0" t="n">
+        <v>345030</v>
       </c>
       <c r="C638" s="0" t="s">
-        <v>4</v>
+        <v>1225</v>
       </c>
       <c r="D638" s="0" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A639" s="0" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B639" s="0" t="n">
-        <v>357130</v>
+        <v>4</v>
+      </c>
+      <c r="B639" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C639" s="0" t="s">
-        <v>1226</v>
+        <v>4</v>
       </c>
       <c r="D639" s="0" t="s">
         <v>1226</v>
@@ -15336,24 +15351,24 @@
         <v>1227</v>
       </c>
       <c r="B640" s="0" t="n">
-        <v>290041</v>
+        <v>357130</v>
       </c>
       <c r="C640" s="0" t="s">
         <v>1228</v>
       </c>
       <c r="D640" s="0" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="0" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B641" s="0" t="n">
+        <v>290041</v>
+      </c>
+      <c r="C641" s="0" t="s">
         <v>1230</v>
-      </c>
-      <c r="B641" s="0" t="n">
-        <v>311111</v>
-      </c>
-      <c r="C641" s="0" t="s">
-        <v>1231</v>
       </c>
       <c r="D641" s="0" t="s">
         <v>1231</v>
@@ -15364,7 +15379,7 @@
         <v>1232</v>
       </c>
       <c r="B642" s="0" t="n">
-        <v>344110</v>
+        <v>311111</v>
       </c>
       <c r="C642" s="0" t="s">
         <v>1233</v>
@@ -15378,7 +15393,7 @@
         <v>1234</v>
       </c>
       <c r="B643" s="0" t="n">
-        <v>344090</v>
+        <v>344110</v>
       </c>
       <c r="C643" s="0" t="s">
         <v>1235</v>
@@ -15392,24 +15407,24 @@
         <v>1236</v>
       </c>
       <c r="B644" s="0" t="n">
-        <v>323120</v>
+        <v>344090</v>
       </c>
       <c r="C644" s="0" t="s">
         <v>1237</v>
       </c>
       <c r="D644" s="0" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="0" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B645" s="0" t="n">
+        <v>323120</v>
+      </c>
+      <c r="C645" s="0" t="s">
         <v>1239</v>
-      </c>
-      <c r="B645" s="0" t="n">
-        <v>323110</v>
-      </c>
-      <c r="C645" s="0" t="s">
-        <v>1240</v>
       </c>
       <c r="D645" s="0" t="s">
         <v>1240</v>
@@ -15420,7 +15435,7 @@
         <v>1241</v>
       </c>
       <c r="B646" s="0" t="n">
-        <v>358070</v>
+        <v>323110</v>
       </c>
       <c r="C646" s="0" t="s">
         <v>1242</v>
@@ -15434,7 +15449,7 @@
         <v>1243</v>
       </c>
       <c r="B647" s="0" t="n">
-        <v>360080</v>
+        <v>358070</v>
       </c>
       <c r="C647" s="0" t="s">
         <v>1244</v>
@@ -15448,7 +15463,7 @@
         <v>1245</v>
       </c>
       <c r="B648" s="0" t="n">
-        <v>360090</v>
+        <v>360080</v>
       </c>
       <c r="C648" s="0" t="s">
         <v>1246</v>
@@ -15462,7 +15477,7 @@
         <v>1247</v>
       </c>
       <c r="B649" s="0" t="n">
-        <v>268063</v>
+        <v>360090</v>
       </c>
       <c r="C649" s="0" t="s">
         <v>1248</v>
@@ -15476,38 +15491,38 @@
         <v>1249</v>
       </c>
       <c r="B650" s="0" t="n">
-        <v>221123</v>
+        <v>268063</v>
       </c>
       <c r="C650" s="0" t="s">
         <v>1250</v>
       </c>
       <c r="D650" s="0" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A651" s="0" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B651" s="0" t="n">
+        <v>221123</v>
+      </c>
+      <c r="C651" s="0" t="s">
         <v>1252</v>
       </c>
-      <c r="B651" s="0" t="n">
-        <v>290100</v>
-      </c>
-      <c r="C651" s="0" t="s">
+      <c r="D651" s="0" t="s">
         <v>1253</v>
-      </c>
-      <c r="D651" s="0" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A652" s="0" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B652" s="0" t="n">
+        <v>290100</v>
+      </c>
+      <c r="C652" s="0" t="s">
         <v>1255</v>
-      </c>
-      <c r="B652" s="0" t="n">
-        <v>342130</v>
-      </c>
-      <c r="C652" s="0" t="s">
-        <v>1256</v>
       </c>
       <c r="D652" s="0" t="s">
         <v>1256</v>
@@ -15518,7 +15533,7 @@
         <v>1257</v>
       </c>
       <c r="B653" s="0" t="n">
-        <v>223060</v>
+        <v>342130</v>
       </c>
       <c r="C653" s="0" t="s">
         <v>1258</v>
@@ -15529,27 +15544,27 @@
     </row>
     <row r="654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A654" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B654" s="0" t="s">
-        <v>4</v>
+        <v>1259</v>
+      </c>
+      <c r="B654" s="0" t="n">
+        <v>223060</v>
       </c>
       <c r="C654" s="0" t="s">
-        <v>4</v>
+        <v>1260</v>
       </c>
       <c r="D654" s="0" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A655" s="0" t="s">
-        <v>1260</v>
-      </c>
-      <c r="B655" s="0" t="n">
-        <v>263251</v>
+        <v>4</v>
+      </c>
+      <c r="B655" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C655" s="0" t="s">
-        <v>1261</v>
+        <v>4</v>
       </c>
       <c r="D655" s="0" t="s">
         <v>1261</v>
@@ -15560,7 +15575,7 @@
         <v>1262</v>
       </c>
       <c r="B656" s="0" t="n">
-        <v>271070</v>
+        <v>263251</v>
       </c>
       <c r="C656" s="0" t="s">
         <v>1263</v>
@@ -15574,7 +15589,7 @@
         <v>1264</v>
       </c>
       <c r="B657" s="0" t="n">
-        <v>300060</v>
+        <v>271070</v>
       </c>
       <c r="C657" s="0" t="s">
         <v>1265</v>
@@ -15585,27 +15600,27 @@
     </row>
     <row r="658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A658" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B658" s="0" t="s">
-        <v>4</v>
+        <v>1266</v>
+      </c>
+      <c r="B658" s="0" t="n">
+        <v>300060</v>
       </c>
       <c r="C658" s="0" t="s">
-        <v>4</v>
+        <v>1267</v>
       </c>
       <c r="D658" s="0" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A659" s="0" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B659" s="0" t="n">
-        <v>221101</v>
+        <v>4</v>
+      </c>
+      <c r="B659" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C659" s="0" t="s">
-        <v>1268</v>
+        <v>4</v>
       </c>
       <c r="D659" s="0" t="s">
         <v>1268</v>
@@ -15613,27 +15628,27 @@
     </row>
     <row r="660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A660" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B660" s="0" t="s">
-        <v>4</v>
+        <v>1269</v>
+      </c>
+      <c r="B660" s="0" t="n">
+        <v>221101</v>
       </c>
       <c r="C660" s="0" t="s">
-        <v>4</v>
+        <v>1270</v>
       </c>
       <c r="D660" s="0" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A661" s="0" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B661" s="0" t="n">
-        <v>222040</v>
+        <v>4</v>
+      </c>
+      <c r="B661" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C661" s="0" t="s">
-        <v>1271</v>
+        <v>4</v>
       </c>
       <c r="D661" s="0" t="s">
         <v>1271</v>
@@ -15641,27 +15656,27 @@
     </row>
     <row r="662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A662" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B662" s="0" t="s">
-        <v>4</v>
+        <v>1272</v>
+      </c>
+      <c r="B662" s="0" t="n">
+        <v>222040</v>
       </c>
       <c r="C662" s="0" t="s">
-        <v>4</v>
+        <v>1273</v>
       </c>
       <c r="D662" s="0" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A663" s="0" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B663" s="0" t="n">
-        <v>341095</v>
+        <v>4</v>
+      </c>
+      <c r="B663" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C663" s="0" t="s">
-        <v>1274</v>
+        <v>4</v>
       </c>
       <c r="D663" s="0" t="s">
         <v>1274</v>
@@ -15669,16 +15684,16 @@
     </row>
     <row r="664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A664" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B664" s="0" t="s">
-        <v>4</v>
+        <v>1275</v>
+      </c>
+      <c r="B664" s="0" t="n">
+        <v>341095</v>
       </c>
       <c r="C664" s="0" t="s">
-        <v>4</v>
+        <v>1276</v>
       </c>
       <c r="D664" s="0" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15692,18 +15707,18 @@
         <v>4</v>
       </c>
       <c r="D665" s="0" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A666" s="0" t="s">
-        <v>1277</v>
-      </c>
-      <c r="B666" s="0" t="n">
-        <v>273082</v>
+        <v>4</v>
+      </c>
+      <c r="B666" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C666" s="0" t="s">
-        <v>1278</v>
+        <v>4</v>
       </c>
       <c r="D666" s="0" t="s">
         <v>1278</v>
@@ -15714,7 +15729,7 @@
         <v>1279</v>
       </c>
       <c r="B667" s="0" t="n">
-        <v>320140</v>
+        <v>273082</v>
       </c>
       <c r="C667" s="0" t="s">
         <v>1280</v>
@@ -15728,7 +15743,7 @@
         <v>1281</v>
       </c>
       <c r="B668" s="0" t="n">
-        <v>344092</v>
+        <v>320140</v>
       </c>
       <c r="C668" s="0" t="s">
         <v>1282</v>
@@ -15742,7 +15757,7 @@
         <v>1283</v>
       </c>
       <c r="B669" s="0" t="n">
-        <v>213020</v>
+        <v>344092</v>
       </c>
       <c r="C669" s="0" t="s">
         <v>1284</v>
@@ -15756,7 +15771,7 @@
         <v>1285</v>
       </c>
       <c r="B670" s="0" t="n">
-        <v>354007</v>
+        <v>213020</v>
       </c>
       <c r="C670" s="0" t="s">
         <v>1286</v>
@@ -15770,7 +15785,7 @@
         <v>1287</v>
       </c>
       <c r="B671" s="0" t="n">
-        <v>355125</v>
+        <v>354007</v>
       </c>
       <c r="C671" s="0" t="s">
         <v>1288</v>
@@ -15784,7 +15799,7 @@
         <v>1289</v>
       </c>
       <c r="B672" s="0" t="n">
-        <v>351050</v>
+        <v>355125</v>
       </c>
       <c r="C672" s="0" t="s">
         <v>1290</v>
@@ -15798,24 +15813,24 @@
         <v>1291</v>
       </c>
       <c r="B673" s="0" t="n">
-        <v>357063</v>
+        <v>351050</v>
       </c>
       <c r="C673" s="0" t="s">
         <v>1292</v>
       </c>
       <c r="D673" s="0" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A674" s="0" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B674" s="0" t="n">
+        <v>357063</v>
+      </c>
+      <c r="C674" s="0" t="s">
         <v>1294</v>
-      </c>
-      <c r="B674" s="0" t="n">
-        <v>351020</v>
-      </c>
-      <c r="C674" s="0" t="s">
-        <v>1295</v>
       </c>
       <c r="D674" s="0" t="s">
         <v>1295</v>
@@ -15826,7 +15841,7 @@
         <v>1296</v>
       </c>
       <c r="B675" s="0" t="n">
-        <v>351030</v>
+        <v>351020</v>
       </c>
       <c r="C675" s="0" t="s">
         <v>1297</v>
@@ -15840,7 +15855,7 @@
         <v>1298</v>
       </c>
       <c r="B676" s="0" t="n">
-        <v>341070</v>
+        <v>351030</v>
       </c>
       <c r="C676" s="0" t="s">
         <v>1299</v>
@@ -15854,7 +15869,7 @@
         <v>1300</v>
       </c>
       <c r="B677" s="0" t="n">
-        <v>354060</v>
+        <v>341070</v>
       </c>
       <c r="C677" s="0" t="s">
         <v>1301</v>
@@ -15868,7 +15883,7 @@
         <v>1302</v>
       </c>
       <c r="B678" s="0" t="n">
-        <v>357079</v>
+        <v>354060</v>
       </c>
       <c r="C678" s="0" t="s">
         <v>1303</v>
@@ -15882,7 +15897,7 @@
         <v>1304</v>
       </c>
       <c r="B679" s="0" t="n">
-        <v>355130</v>
+        <v>357079</v>
       </c>
       <c r="C679" s="0" t="s">
         <v>1305</v>
@@ -15896,7 +15911,7 @@
         <v>1306</v>
       </c>
       <c r="B680" s="0" t="n">
-        <v>360040</v>
+        <v>355130</v>
       </c>
       <c r="C680" s="0" t="s">
         <v>1307</v>
@@ -15910,7 +15925,7 @@
         <v>1308</v>
       </c>
       <c r="B681" s="0" t="n">
-        <v>322110</v>
+        <v>360040</v>
       </c>
       <c r="C681" s="0" t="s">
         <v>1309</v>
@@ -15924,7 +15939,7 @@
         <v>1310</v>
       </c>
       <c r="B682" s="0" t="n">
-        <v>222164</v>
+        <v>322110</v>
       </c>
       <c r="C682" s="0" t="s">
         <v>1311</v>
@@ -15935,16 +15950,16 @@
     </row>
     <row r="683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A683" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B683" s="0" t="s">
-        <v>4</v>
+        <v>1312</v>
+      </c>
+      <c r="B683" s="0" t="n">
+        <v>222164</v>
       </c>
       <c r="C683" s="0" t="s">
-        <v>4</v>
+        <v>1313</v>
       </c>
       <c r="D683" s="0" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15958,7 +15973,7 @@
         <v>4</v>
       </c>
       <c r="D684" s="0" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15972,7 +15987,7 @@
         <v>4</v>
       </c>
       <c r="D685" s="0" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15986,18 +16001,18 @@
         <v>4</v>
       </c>
       <c r="D686" s="0" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A687" s="0" t="s">
-        <v>1316</v>
-      </c>
-      <c r="B687" s="0" t="n">
-        <v>290060</v>
+        <v>4</v>
+      </c>
+      <c r="B687" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C687" s="0" t="s">
-        <v>1317</v>
+        <v>4</v>
       </c>
       <c r="D687" s="0" t="s">
         <v>1317</v>
@@ -16008,7 +16023,7 @@
         <v>1318</v>
       </c>
       <c r="B688" s="0" t="n">
-        <v>212050</v>
+        <v>290060</v>
       </c>
       <c r="C688" s="0" t="s">
         <v>1319</v>
@@ -16019,27 +16034,27 @@
     </row>
     <row r="689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A689" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B689" s="0" t="s">
-        <v>4</v>
+        <v>1320</v>
+      </c>
+      <c r="B689" s="0" t="n">
+        <v>212050</v>
       </c>
       <c r="C689" s="0" t="s">
-        <v>4</v>
+        <v>1321</v>
       </c>
       <c r="D689" s="0" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A690" s="0" t="s">
-        <v>1321</v>
-      </c>
-      <c r="B690" s="0" t="n">
-        <v>222001</v>
+        <v>4</v>
+      </c>
+      <c r="B690" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C690" s="0" t="s">
-        <v>1322</v>
+        <v>4</v>
       </c>
       <c r="D690" s="0" t="s">
         <v>1322</v>
@@ -16050,7 +16065,7 @@
         <v>1323</v>
       </c>
       <c r="B691" s="0" t="n">
-        <v>312180</v>
+        <v>222001</v>
       </c>
       <c r="C691" s="0" t="s">
         <v>1324</v>
@@ -16061,27 +16076,27 @@
     </row>
     <row r="692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A692" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B692" s="0" t="s">
-        <v>4</v>
+        <v>1325</v>
+      </c>
+      <c r="B692" s="0" t="n">
+        <v>312180</v>
       </c>
       <c r="C692" s="0" t="s">
-        <v>4</v>
+        <v>1326</v>
       </c>
       <c r="D692" s="0" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A693" s="0" t="s">
-        <v>1326</v>
-      </c>
-      <c r="B693" s="0" t="n">
-        <v>222056</v>
+        <v>4</v>
+      </c>
+      <c r="B693" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C693" s="0" t="s">
-        <v>1327</v>
+        <v>4</v>
       </c>
       <c r="D693" s="0" t="s">
         <v>1327</v>
@@ -16092,7 +16107,7 @@
         <v>1328</v>
       </c>
       <c r="B694" s="0" t="n">
-        <v>223020</v>
+        <v>222056</v>
       </c>
       <c r="C694" s="0" t="s">
         <v>1329</v>
@@ -16106,7 +16121,7 @@
         <v>1330</v>
       </c>
       <c r="B695" s="0" t="n">
-        <v>223030</v>
+        <v>223020</v>
       </c>
       <c r="C695" s="0" t="s">
         <v>1331</v>
@@ -16120,7 +16135,7 @@
         <v>1332</v>
       </c>
       <c r="B696" s="0" t="n">
-        <v>300650</v>
+        <v>223030</v>
       </c>
       <c r="C696" s="0" t="s">
         <v>1333</v>
@@ -16133,45 +16148,45 @@
       <c r="A697" s="0" t="s">
         <v>1334</v>
       </c>
-      <c r="B697" s="0" t="s">
+      <c r="B697" s="0" t="n">
+        <v>300650</v>
+      </c>
+      <c r="C697" s="0" t="s">
         <v>1335</v>
       </c>
-      <c r="C697" s="0" t="n">
-        <v>221280</v>
-      </c>
       <c r="D697" s="0" t="s">
-        <v>1336</v>
-      </c>
-      <c r="E697" s="0" t="s">
-        <v>1337</v>
-      </c>
-      <c r="F697" s="0" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A698" s="0" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B698" s="0" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C698" s="0" t="n">
+        <v>221280</v>
+      </c>
+      <c r="D698" s="0" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E698" s="0" t="s">
         <v>1339</v>
       </c>
-      <c r="B698" s="0" t="n">
-        <v>290072</v>
-      </c>
-      <c r="C698" s="0" t="s">
+      <c r="F698" s="0" t="s">
         <v>1340</v>
-      </c>
-      <c r="D698" s="0" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A699" s="0" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B699" s="0" t="n">
+        <v>290072</v>
+      </c>
+      <c r="C699" s="0" t="s">
         <v>1342</v>
-      </c>
-      <c r="B699" s="0" t="n">
-        <v>241050</v>
-      </c>
-      <c r="C699" s="0" t="s">
-        <v>1343</v>
       </c>
       <c r="D699" s="0" t="s">
         <v>1343</v>
@@ -16179,27 +16194,27 @@
     </row>
     <row r="700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A700" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B700" s="0" t="s">
-        <v>4</v>
+        <v>1344</v>
+      </c>
+      <c r="B700" s="0" t="n">
+        <v>241050</v>
       </c>
       <c r="C700" s="0" t="s">
-        <v>4</v>
+        <v>1345</v>
       </c>
       <c r="D700" s="0" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A701" s="0" t="s">
-        <v>1345</v>
-      </c>
-      <c r="B701" s="0" t="n">
-        <v>311290</v>
+        <v>4</v>
+      </c>
+      <c r="B701" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C701" s="0" t="s">
-        <v>1346</v>
+        <v>4</v>
       </c>
       <c r="D701" s="0" t="s">
         <v>1346</v>
@@ -16210,7 +16225,7 @@
         <v>1347</v>
       </c>
       <c r="B702" s="0" t="n">
-        <v>224030</v>
+        <v>311290</v>
       </c>
       <c r="C702" s="0" t="s">
         <v>1348</v>
@@ -16224,7 +16239,7 @@
         <v>1349</v>
       </c>
       <c r="B703" s="0" t="n">
-        <v>355050</v>
+        <v>224030</v>
       </c>
       <c r="C703" s="0" t="s">
         <v>1350</v>
@@ -16238,7 +16253,7 @@
         <v>1351</v>
       </c>
       <c r="B704" s="0" t="n">
-        <v>222080</v>
+        <v>355050</v>
       </c>
       <c r="C704" s="0" t="s">
         <v>1352</v>
@@ -16252,7 +16267,7 @@
         <v>1353</v>
       </c>
       <c r="B705" s="0" t="n">
-        <v>222120</v>
+        <v>222080</v>
       </c>
       <c r="C705" s="0" t="s">
         <v>1354</v>
@@ -16266,7 +16281,7 @@
         <v>1355</v>
       </c>
       <c r="B706" s="0" t="n">
-        <v>222090</v>
+        <v>222120</v>
       </c>
       <c r="C706" s="0" t="s">
         <v>1356</v>
@@ -16280,7 +16295,7 @@
         <v>1357</v>
       </c>
       <c r="B707" s="0" t="n">
-        <v>222055</v>
+        <v>222090</v>
       </c>
       <c r="C707" s="0" t="s">
         <v>1358</v>
@@ -16294,7 +16309,7 @@
         <v>1359</v>
       </c>
       <c r="B708" s="0" t="n">
-        <v>300052</v>
+        <v>222055</v>
       </c>
       <c r="C708" s="0" t="s">
         <v>1360</v>
@@ -16308,24 +16323,24 @@
         <v>1361</v>
       </c>
       <c r="B709" s="0" t="n">
-        <v>355060</v>
+        <v>300052</v>
       </c>
       <c r="C709" s="0" t="s">
         <v>1362</v>
       </c>
       <c r="D709" s="0" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A710" s="0" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B710" s="0" t="n">
+        <v>355060</v>
+      </c>
+      <c r="C710" s="0" t="s">
         <v>1364</v>
-      </c>
-      <c r="B710" s="0" t="n">
-        <v>210030</v>
-      </c>
-      <c r="C710" s="0" t="s">
-        <v>1365</v>
       </c>
       <c r="D710" s="0" t="s">
         <v>1365</v>
@@ -16333,16 +16348,16 @@
     </row>
     <row r="711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A711" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B711" s="0" t="s">
-        <v>4</v>
+        <v>1366</v>
+      </c>
+      <c r="B711" s="0" t="n">
+        <v>210030</v>
       </c>
       <c r="C711" s="0" t="s">
-        <v>4</v>
+        <v>1367</v>
       </c>
       <c r="D711" s="0" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16356,18 +16371,18 @@
         <v>4</v>
       </c>
       <c r="D712" s="0" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A713" s="0" t="s">
-        <v>1368</v>
-      </c>
-      <c r="B713" s="0" t="n">
-        <v>300080</v>
+        <v>4</v>
+      </c>
+      <c r="B713" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C713" s="0" t="s">
-        <v>1369</v>
+        <v>4</v>
       </c>
       <c r="D713" s="0" t="s">
         <v>1369</v>
@@ -16378,7 +16393,7 @@
         <v>1370</v>
       </c>
       <c r="B714" s="0" t="n">
-        <v>374010</v>
+        <v>300080</v>
       </c>
       <c r="C714" s="0" t="s">
         <v>1371</v>
@@ -16392,27 +16407,27 @@
         <v>1372</v>
       </c>
       <c r="B715" s="0" t="n">
-        <v>345010</v>
+        <v>374010</v>
       </c>
       <c r="C715" s="0" t="s">
         <v>1373</v>
       </c>
       <c r="D715" s="0" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A716" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B716" s="0" t="s">
-        <v>4</v>
+        <v>1374</v>
+      </c>
+      <c r="B716" s="0" t="n">
+        <v>345010</v>
       </c>
       <c r="C716" s="0" t="s">
-        <v>4</v>
+        <v>1375</v>
       </c>
       <c r="D716" s="0" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16426,18 +16441,18 @@
         <v>4</v>
       </c>
       <c r="D717" s="0" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="718" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A718" s="0" t="s">
-        <v>1377</v>
-      </c>
-      <c r="B718" s="0" t="n">
-        <v>358010</v>
+        <v>4</v>
+      </c>
+      <c r="B718" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C718" s="0" t="s">
-        <v>1378</v>
+        <v>4</v>
       </c>
       <c r="D718" s="0" t="s">
         <v>1378</v>
@@ -16448,7 +16463,7 @@
         <v>1379</v>
       </c>
       <c r="B719" s="0" t="n">
-        <v>300055</v>
+        <v>358010</v>
       </c>
       <c r="C719" s="0" t="s">
         <v>1380</v>
@@ -16462,7 +16477,7 @@
         <v>1381</v>
       </c>
       <c r="B720" s="0" t="n">
-        <v>300680</v>
+        <v>300055</v>
       </c>
       <c r="C720" s="0" t="s">
         <v>1382</v>
@@ -16476,7 +16491,7 @@
         <v>1383</v>
       </c>
       <c r="B721" s="0" t="n">
-        <v>300056</v>
+        <v>300680</v>
       </c>
       <c r="C721" s="0" t="s">
         <v>1384</v>
@@ -16490,7 +16505,7 @@
         <v>1385</v>
       </c>
       <c r="B722" s="0" t="n">
-        <v>300051</v>
+        <v>300056</v>
       </c>
       <c r="C722" s="0" t="s">
         <v>1386</v>
@@ -16504,7 +16519,7 @@
         <v>1387</v>
       </c>
       <c r="B723" s="0" t="n">
-        <v>342110</v>
+        <v>300051</v>
       </c>
       <c r="C723" s="0" t="s">
         <v>1388</v>
@@ -16518,7 +16533,7 @@
         <v>1389</v>
       </c>
       <c r="B724" s="0" t="n">
-        <v>222053</v>
+        <v>342110</v>
       </c>
       <c r="C724" s="0" t="s">
         <v>1390</v>
@@ -16532,7 +16547,7 @@
         <v>1391</v>
       </c>
       <c r="B725" s="0" t="n">
-        <v>357022</v>
+        <v>222053</v>
       </c>
       <c r="C725" s="0" t="s">
         <v>1392</v>
@@ -16546,7 +16561,7 @@
         <v>1393</v>
       </c>
       <c r="B726" s="0" t="n">
-        <v>264150</v>
+        <v>357022</v>
       </c>
       <c r="C726" s="0" t="s">
         <v>1394</v>
@@ -16560,7 +16575,7 @@
         <v>1395</v>
       </c>
       <c r="B727" s="0" t="n">
-        <v>355042</v>
+        <v>264150</v>
       </c>
       <c r="C727" s="0" t="s">
         <v>1396</v>
@@ -16574,7 +16589,7 @@
         <v>1397</v>
       </c>
       <c r="B728" s="0" t="n">
-        <v>211041</v>
+        <v>355042</v>
       </c>
       <c r="C728" s="0" t="s">
         <v>1398</v>
@@ -16588,7 +16603,7 @@
         <v>1399</v>
       </c>
       <c r="B729" s="0" t="n">
-        <v>211071</v>
+        <v>211041</v>
       </c>
       <c r="C729" s="0" t="s">
         <v>1400</v>
@@ -16602,7 +16617,7 @@
         <v>1401</v>
       </c>
       <c r="B730" s="0" t="n">
-        <v>263100</v>
+        <v>211071</v>
       </c>
       <c r="C730" s="0" t="s">
         <v>1402</v>
@@ -16616,7 +16631,7 @@
         <v>1403</v>
       </c>
       <c r="B731" s="0" t="n">
-        <v>341081</v>
+        <v>263100</v>
       </c>
       <c r="C731" s="0" t="s">
         <v>1404</v>
@@ -16630,7 +16645,7 @@
         <v>1405</v>
       </c>
       <c r="B732" s="0" t="n">
-        <v>355012</v>
+        <v>341081</v>
       </c>
       <c r="C732" s="0" t="s">
         <v>1406</v>
@@ -16644,7 +16659,7 @@
         <v>1407</v>
       </c>
       <c r="B733" s="0" t="n">
-        <v>271011</v>
+        <v>355012</v>
       </c>
       <c r="C733" s="0" t="s">
         <v>1408</v>
@@ -16658,7 +16673,7 @@
         <v>1409</v>
       </c>
       <c r="B734" s="0" t="n">
-        <v>261231</v>
+        <v>271011</v>
       </c>
       <c r="C734" s="0" t="s">
         <v>1410</v>
@@ -16672,7 +16687,7 @@
         <v>1411</v>
       </c>
       <c r="B735" s="0" t="n">
-        <v>273087</v>
+        <v>261231</v>
       </c>
       <c r="C735" s="0" t="s">
         <v>1412</v>
@@ -16686,7 +16701,7 @@
         <v>1413</v>
       </c>
       <c r="B736" s="0" t="n">
-        <v>263070</v>
+        <v>273087</v>
       </c>
       <c r="C736" s="0" t="s">
         <v>1414</v>
@@ -16700,24 +16715,24 @@
         <v>1415</v>
       </c>
       <c r="B737" s="0" t="n">
-        <v>357066</v>
+        <v>263070</v>
       </c>
       <c r="C737" s="0" t="s">
         <v>1416</v>
       </c>
       <c r="D737" s="0" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="738" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A738" s="0" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B738" s="0" t="n">
+        <v>357066</v>
+      </c>
+      <c r="C738" s="0" t="s">
         <v>1418</v>
-      </c>
-      <c r="B738" s="0" t="n">
-        <v>355200</v>
-      </c>
-      <c r="C738" s="0" t="s">
-        <v>1419</v>
       </c>
       <c r="D738" s="0" t="s">
         <v>1419</v>
@@ -16728,7 +16743,7 @@
         <v>1420</v>
       </c>
       <c r="B739" s="0" t="n">
-        <v>263291</v>
+        <v>355200</v>
       </c>
       <c r="C739" s="0" t="s">
         <v>1421</v>
@@ -16742,7 +16757,7 @@
         <v>1422</v>
       </c>
       <c r="B740" s="0" t="n">
-        <v>263040</v>
+        <v>263291</v>
       </c>
       <c r="C740" s="0" t="s">
         <v>1423</v>
@@ -16756,7 +16771,7 @@
         <v>1424</v>
       </c>
       <c r="B741" s="0" t="n">
-        <v>261030</v>
+        <v>263040</v>
       </c>
       <c r="C741" s="0" t="s">
         <v>1425</v>
@@ -16770,7 +16785,7 @@
         <v>1426</v>
       </c>
       <c r="B742" s="0" t="n">
-        <v>382020</v>
+        <v>261030</v>
       </c>
       <c r="C742" s="0" t="s">
         <v>1427</v>
@@ -16784,7 +16799,7 @@
         <v>1428</v>
       </c>
       <c r="B743" s="0" t="n">
-        <v>341100</v>
+        <v>382020</v>
       </c>
       <c r="C743" s="0" t="s">
         <v>1429</v>
@@ -16798,7 +16813,7 @@
         <v>1430</v>
       </c>
       <c r="B744" s="0" t="n">
-        <v>341001</v>
+        <v>341100</v>
       </c>
       <c r="C744" s="0" t="s">
         <v>1431</v>
@@ -16812,7 +16827,7 @@
         <v>1432</v>
       </c>
       <c r="B745" s="0" t="n">
-        <v>273083</v>
+        <v>341001</v>
       </c>
       <c r="C745" s="0" t="s">
         <v>1433</v>
@@ -16826,7 +16841,7 @@
         <v>1434</v>
       </c>
       <c r="B746" s="0" t="n">
-        <v>300054</v>
+        <v>273083</v>
       </c>
       <c r="C746" s="0" t="s">
         <v>1435</v>
@@ -16840,24 +16855,24 @@
         <v>1436</v>
       </c>
       <c r="B747" s="0" t="n">
-        <v>357040</v>
+        <v>300054</v>
       </c>
       <c r="C747" s="0" t="s">
         <v>1437</v>
       </c>
       <c r="D747" s="0" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="748" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A748" s="0" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B748" s="0" t="n">
+        <v>357040</v>
+      </c>
+      <c r="C748" s="0" t="s">
         <v>1439</v>
-      </c>
-      <c r="B748" s="0" t="n">
-        <v>345034</v>
-      </c>
-      <c r="C748" s="0" t="s">
-        <v>1440</v>
       </c>
       <c r="D748" s="0" t="s">
         <v>1440</v>
@@ -16868,7 +16883,7 @@
         <v>1441</v>
       </c>
       <c r="B749" s="0" t="n">
-        <v>300310</v>
+        <v>345034</v>
       </c>
       <c r="C749" s="0" t="s">
         <v>1442</v>
@@ -16882,7 +16897,7 @@
         <v>1443</v>
       </c>
       <c r="B750" s="0" t="n">
-        <v>345040</v>
+        <v>300310</v>
       </c>
       <c r="C750" s="0" t="s">
         <v>1444</v>
@@ -16896,13 +16911,13 @@
         <v>1445</v>
       </c>
       <c r="B751" s="0" t="n">
-        <v>345050</v>
+        <v>345040</v>
       </c>
       <c r="C751" s="0" t="s">
         <v>1446</v>
       </c>
       <c r="D751" s="0" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16910,38 +16925,38 @@
         <v>1447</v>
       </c>
       <c r="B752" s="0" t="n">
-        <v>273020</v>
+        <v>345050</v>
       </c>
       <c r="C752" s="0" t="s">
         <v>1448</v>
       </c>
       <c r="D752" s="0" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A753" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B753" s="0" t="s">
-        <v>4</v>
+        <v>1449</v>
+      </c>
+      <c r="B753" s="0" t="n">
+        <v>273020</v>
       </c>
       <c r="C753" s="0" t="s">
-        <v>4</v>
+        <v>1450</v>
       </c>
       <c r="D753" s="0" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A754" s="0" t="s">
-        <v>1450</v>
-      </c>
-      <c r="B754" s="0" t="n">
-        <v>300470</v>
+        <v>4</v>
+      </c>
+      <c r="B754" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C754" s="0" t="s">
-        <v>1451</v>
+        <v>4</v>
       </c>
       <c r="D754" s="0" t="s">
         <v>1451</v>
@@ -16952,24 +16967,24 @@
         <v>1452</v>
       </c>
       <c r="B755" s="0" t="n">
-        <v>341090</v>
+        <v>300470</v>
       </c>
       <c r="C755" s="0" t="s">
         <v>1453</v>
       </c>
       <c r="D755" s="0" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A756" s="0" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B756" s="0" t="n">
+        <v>341090</v>
+      </c>
+      <c r="C756" s="0" t="s">
         <v>1455</v>
-      </c>
-      <c r="B756" s="0" t="n">
-        <v>214090</v>
-      </c>
-      <c r="C756" s="0" t="s">
-        <v>1456</v>
       </c>
       <c r="D756" s="0" t="s">
         <v>1456</v>
@@ -16980,7 +16995,7 @@
         <v>1457</v>
       </c>
       <c r="B757" s="0" t="n">
-        <v>371070</v>
+        <v>214090</v>
       </c>
       <c r="C757" s="0" t="s">
         <v>1458</v>
@@ -16994,7 +17009,7 @@
         <v>1459</v>
       </c>
       <c r="B758" s="0" t="n">
-        <v>290190</v>
+        <v>371070</v>
       </c>
       <c r="C758" s="0" t="s">
         <v>1460</v>
@@ -17008,7 +17023,7 @@
         <v>1461</v>
       </c>
       <c r="B759" s="0" t="n">
-        <v>355107</v>
+        <v>290190</v>
       </c>
       <c r="C759" s="0" t="s">
         <v>1462</v>
@@ -17022,7 +17037,7 @@
         <v>1463</v>
       </c>
       <c r="B760" s="0" t="n">
-        <v>263010</v>
+        <v>355107</v>
       </c>
       <c r="C760" s="0" t="s">
         <v>1464</v>
@@ -17036,7 +17051,7 @@
         <v>1465</v>
       </c>
       <c r="B761" s="0" t="n">
-        <v>352011</v>
+        <v>263010</v>
       </c>
       <c r="C761" s="0" t="s">
         <v>1466</v>
@@ -17050,38 +17065,38 @@
         <v>1467</v>
       </c>
       <c r="B762" s="0" t="n">
-        <v>357160</v>
+        <v>352011</v>
       </c>
       <c r="C762" s="0" t="s">
         <v>1468</v>
       </c>
       <c r="D762" s="0" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="763" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A763" s="0" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B763" s="0" t="n">
+        <v>357160</v>
+      </c>
+      <c r="C763" s="0" t="s">
         <v>1470</v>
       </c>
-      <c r="B763" s="0" t="n">
-        <v>351060</v>
-      </c>
-      <c r="C763" s="0" t="s">
+      <c r="D763" s="0" t="s">
         <v>1471</v>
-      </c>
-      <c r="D763" s="0" t="s">
-        <v>1472</v>
       </c>
     </row>
     <row r="764" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A764" s="0" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B764" s="0" t="n">
+        <v>351060</v>
+      </c>
+      <c r="C764" s="0" t="s">
         <v>1473</v>
-      </c>
-      <c r="B764" s="0" t="n">
-        <v>355094</v>
-      </c>
-      <c r="C764" s="0" t="s">
-        <v>1474</v>
       </c>
       <c r="D764" s="0" t="s">
         <v>1474</v>
@@ -17092,7 +17107,7 @@
         <v>1475</v>
       </c>
       <c r="B765" s="0" t="n">
-        <v>355090</v>
+        <v>355094</v>
       </c>
       <c r="C765" s="0" t="s">
         <v>1476</v>
@@ -17106,24 +17121,24 @@
         <v>1477</v>
       </c>
       <c r="B766" s="0" t="n">
-        <v>357150</v>
+        <v>355090</v>
       </c>
       <c r="C766" s="0" t="s">
         <v>1478</v>
       </c>
       <c r="D766" s="0" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="767" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A767" s="0" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B767" s="0" t="n">
+        <v>357150</v>
+      </c>
+      <c r="C767" s="0" t="s">
         <v>1480</v>
-      </c>
-      <c r="B767" s="0" t="n">
-        <v>358053</v>
-      </c>
-      <c r="C767" s="0" t="s">
-        <v>1481</v>
       </c>
       <c r="D767" s="0" t="s">
         <v>1481</v>
@@ -17134,7 +17149,7 @@
         <v>1482</v>
       </c>
       <c r="B768" s="0" t="n">
-        <v>360140</v>
+        <v>358053</v>
       </c>
       <c r="C768" s="0" t="s">
         <v>1483</v>
@@ -17148,7 +17163,7 @@
         <v>1484</v>
       </c>
       <c r="B769" s="0" t="n">
-        <v>357121</v>
+        <v>360140</v>
       </c>
       <c r="C769" s="0" t="s">
         <v>1485</v>
@@ -17162,7 +17177,7 @@
         <v>1486</v>
       </c>
       <c r="B770" s="0" t="n">
-        <v>342210</v>
+        <v>357121</v>
       </c>
       <c r="C770" s="0" t="s">
         <v>1487</v>
@@ -17176,7 +17191,7 @@
         <v>1488</v>
       </c>
       <c r="B771" s="0" t="n">
-        <v>352060</v>
+        <v>342210</v>
       </c>
       <c r="C771" s="0" t="s">
         <v>1489</v>
@@ -17190,7 +17205,7 @@
         <v>1490</v>
       </c>
       <c r="B772" s="0" t="n">
-        <v>354000</v>
+        <v>352060</v>
       </c>
       <c r="C772" s="0" t="s">
         <v>1491</v>
@@ -17201,27 +17216,27 @@
     </row>
     <row r="773" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A773" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B773" s="0" t="s">
-        <v>4</v>
+        <v>1492</v>
+      </c>
+      <c r="B773" s="0" t="n">
+        <v>354000</v>
       </c>
       <c r="C773" s="0" t="s">
-        <v>4</v>
+        <v>1493</v>
       </c>
       <c r="D773" s="0" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="774" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A774" s="0" t="s">
-        <v>1493</v>
-      </c>
-      <c r="B774" s="0" t="n">
-        <v>271060</v>
+        <v>4</v>
+      </c>
+      <c r="B774" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C774" s="0" t="s">
-        <v>1494</v>
+        <v>4</v>
       </c>
       <c r="D774" s="0" t="s">
         <v>1494</v>
@@ -17232,7 +17247,7 @@
         <v>1495</v>
       </c>
       <c r="B775" s="0" t="n">
-        <v>321030</v>
+        <v>271060</v>
       </c>
       <c r="C775" s="0" t="s">
         <v>1496</v>
@@ -17246,7 +17261,7 @@
         <v>1497</v>
       </c>
       <c r="B776" s="0" t="n">
-        <v>261290</v>
+        <v>321030</v>
       </c>
       <c r="C776" s="0" t="s">
         <v>1498</v>
@@ -17260,24 +17275,24 @@
         <v>1499</v>
       </c>
       <c r="B777" s="0" t="n">
-        <v>290110</v>
+        <v>261290</v>
       </c>
       <c r="C777" s="0" t="s">
         <v>1500</v>
       </c>
       <c r="D777" s="0" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="778" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A778" s="0" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B778" s="0" t="n">
+        <v>290110</v>
+      </c>
+      <c r="C778" s="0" t="s">
         <v>1502</v>
-      </c>
-      <c r="B778" s="0" t="n">
-        <v>264071</v>
-      </c>
-      <c r="C778" s="0" t="s">
-        <v>1503</v>
       </c>
       <c r="D778" s="0" t="s">
         <v>1503</v>
@@ -17288,7 +17303,7 @@
         <v>1504</v>
       </c>
       <c r="B779" s="0" t="n">
-        <v>261251</v>
+        <v>264071</v>
       </c>
       <c r="C779" s="0" t="s">
         <v>1505</v>
@@ -17302,7 +17317,7 @@
         <v>1506</v>
       </c>
       <c r="B780" s="0" t="n">
-        <v>263340</v>
+        <v>261251</v>
       </c>
       <c r="C780" s="0" t="s">
         <v>1507</v>
@@ -17313,41 +17328,41 @@
     </row>
     <row r="781" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A781" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B781" s="0" t="s">
-        <v>4</v>
+        <v>1508</v>
+      </c>
+      <c r="B781" s="0" t="n">
+        <v>263340</v>
       </c>
       <c r="C781" s="0" t="s">
-        <v>4</v>
+        <v>1509</v>
       </c>
       <c r="D781" s="0" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="782" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A782" s="0" t="s">
-        <v>1509</v>
-      </c>
-      <c r="B782" s="0" t="n">
-        <v>2290020</v>
+        <v>4</v>
+      </c>
+      <c r="B782" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C782" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D782" s="0" t="s">
         <v>1510</v>
-      </c>
-      <c r="D782" s="0" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="783" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A783" s="0" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B783" s="0" t="n">
+        <v>2290020</v>
+      </c>
+      <c r="C783" s="0" t="s">
         <v>1512</v>
-      </c>
-      <c r="B783" s="0" t="n">
-        <v>358063</v>
-      </c>
-      <c r="C783" s="0" t="s">
-        <v>1513</v>
       </c>
       <c r="D783" s="0" t="s">
         <v>1513</v>
@@ -17355,27 +17370,27 @@
     </row>
     <row r="784" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A784" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B784" s="0" t="s">
-        <v>4</v>
+        <v>1514</v>
+      </c>
+      <c r="B784" s="0" t="n">
+        <v>358063</v>
       </c>
       <c r="C784" s="0" t="s">
-        <v>4</v>
+        <v>1515</v>
       </c>
       <c r="D784" s="0" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="785" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A785" s="0" t="s">
-        <v>1515</v>
-      </c>
-      <c r="B785" s="0" t="n">
-        <v>241040</v>
+        <v>4</v>
+      </c>
+      <c r="B785" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C785" s="0" t="s">
-        <v>1516</v>
+        <v>4</v>
       </c>
       <c r="D785" s="0" t="s">
         <v>1516</v>
@@ -17386,7 +17401,7 @@
         <v>1517</v>
       </c>
       <c r="B786" s="0" t="n">
-        <v>357065</v>
+        <v>241040</v>
       </c>
       <c r="C786" s="0" t="s">
         <v>1518</v>
@@ -17400,7 +17415,7 @@
         <v>1519</v>
       </c>
       <c r="B787" s="0" t="n">
-        <v>352010</v>
+        <v>357065</v>
       </c>
       <c r="C787" s="0" t="s">
         <v>1520</v>
@@ -17414,7 +17429,7 @@
         <v>1521</v>
       </c>
       <c r="B788" s="0" t="n">
-        <v>371020</v>
+        <v>352010</v>
       </c>
       <c r="C788" s="0" t="s">
         <v>1522</v>
@@ -17428,7 +17443,7 @@
         <v>1523</v>
       </c>
       <c r="B789" s="0" t="n">
-        <v>266040</v>
+        <v>371020</v>
       </c>
       <c r="C789" s="0" t="s">
         <v>1524</v>
@@ -17442,24 +17457,24 @@
         <v>1525</v>
       </c>
       <c r="B790" s="0" t="n">
-        <v>345020</v>
+        <v>266040</v>
       </c>
       <c r="C790" s="0" t="s">
         <v>1526</v>
       </c>
       <c r="D790" s="0" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="791" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A791" s="0" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B791" s="0" t="n">
+        <v>345020</v>
+      </c>
+      <c r="C791" s="0" t="s">
         <v>1528</v>
-      </c>
-      <c r="B791" s="0" t="n">
-        <v>264030</v>
-      </c>
-      <c r="C791" s="0" t="s">
-        <v>1529</v>
       </c>
       <c r="D791" s="0" t="s">
         <v>1529</v>
@@ -17470,7 +17485,7 @@
         <v>1530</v>
       </c>
       <c r="B792" s="0" t="n">
-        <v>357024</v>
+        <v>264030</v>
       </c>
       <c r="C792" s="0" t="s">
         <v>1531</v>
@@ -17481,27 +17496,27 @@
     </row>
     <row r="793" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A793" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B793" s="0" t="s">
-        <v>4</v>
+        <v>1532</v>
+      </c>
+      <c r="B793" s="0" t="n">
+        <v>357024</v>
       </c>
       <c r="C793" s="0" t="s">
-        <v>4</v>
+        <v>1533</v>
       </c>
       <c r="D793" s="0" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="794" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A794" s="0" t="s">
-        <v>1533</v>
-      </c>
-      <c r="B794" s="0" t="n">
-        <v>300340</v>
+        <v>4</v>
+      </c>
+      <c r="B794" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C794" s="0" t="s">
-        <v>1534</v>
+        <v>4</v>
       </c>
       <c r="D794" s="0" t="s">
         <v>1534</v>
@@ -17512,7 +17527,7 @@
         <v>1535</v>
       </c>
       <c r="B795" s="0" t="n">
-        <v>351011</v>
+        <v>300340</v>
       </c>
       <c r="C795" s="0" t="s">
         <v>1536</v>
@@ -17526,7 +17541,7 @@
         <v>1537</v>
       </c>
       <c r="B796" s="0" t="n">
-        <v>344060</v>
+        <v>351011</v>
       </c>
       <c r="C796" s="0" t="s">
         <v>1538</v>
@@ -17540,7 +17555,7 @@
         <v>1539</v>
       </c>
       <c r="B797" s="0" t="n">
-        <v>241100</v>
+        <v>344060</v>
       </c>
       <c r="C797" s="0" t="s">
         <v>1540</v>
@@ -17554,7 +17569,7 @@
         <v>1541</v>
       </c>
       <c r="B798" s="0" t="n">
-        <v>290091</v>
+        <v>241100</v>
       </c>
       <c r="C798" s="0" t="s">
         <v>1542</v>
@@ -17568,7 +17583,7 @@
         <v>1543</v>
       </c>
       <c r="B799" s="0" t="n">
-        <v>290112</v>
+        <v>290091</v>
       </c>
       <c r="C799" s="0" t="s">
         <v>1544</v>
@@ -17582,7 +17597,7 @@
         <v>1545</v>
       </c>
       <c r="B800" s="0" t="n">
-        <v>222166</v>
+        <v>290112</v>
       </c>
       <c r="C800" s="0" t="s">
         <v>1546</v>
@@ -17596,24 +17611,24 @@
         <v>1547</v>
       </c>
       <c r="B801" s="0" t="n">
-        <v>290021</v>
+        <v>222166</v>
       </c>
       <c r="C801" s="0" t="s">
         <v>1548</v>
       </c>
       <c r="D801" s="0" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="802" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A802" s="0" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B802" s="0" t="n">
+        <v>290021</v>
+      </c>
+      <c r="C802" s="0" t="s">
         <v>1550</v>
-      </c>
-      <c r="B802" s="0" t="n">
-        <v>232002</v>
-      </c>
-      <c r="C802" s="0" t="s">
-        <v>1551</v>
       </c>
       <c r="D802" s="0" t="s">
         <v>1551</v>
@@ -17624,7 +17639,7 @@
         <v>1552</v>
       </c>
       <c r="B803" s="0" t="n">
-        <v>354006</v>
+        <v>232002</v>
       </c>
       <c r="C803" s="0" t="s">
         <v>1553</v>
@@ -17638,7 +17653,7 @@
         <v>1554</v>
       </c>
       <c r="B804" s="0" t="n">
-        <v>232001</v>
+        <v>354006</v>
       </c>
       <c r="C804" s="0" t="s">
         <v>1555</v>
@@ -17652,24 +17667,24 @@
         <v>1556</v>
       </c>
       <c r="B805" s="0" t="n">
-        <v>355091</v>
+        <v>232001</v>
       </c>
       <c r="C805" s="0" t="s">
         <v>1557</v>
       </c>
       <c r="D805" s="0" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="806" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A806" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B806" s="0" t="n">
+        <v>355091</v>
+      </c>
+      <c r="C806" s="0" t="s">
         <v>1559</v>
-      </c>
-      <c r="B806" s="0" t="n">
-        <v>263050</v>
-      </c>
-      <c r="C806" s="0" t="s">
-        <v>1560</v>
       </c>
       <c r="D806" s="0" t="s">
         <v>1560</v>
@@ -17680,7 +17695,7 @@
         <v>1561</v>
       </c>
       <c r="B807" s="0" t="n">
-        <v>323200</v>
+        <v>263050</v>
       </c>
       <c r="C807" s="0" t="s">
         <v>1562</v>
@@ -17694,7 +17709,7 @@
         <v>1563</v>
       </c>
       <c r="B808" s="0" t="n">
-        <v>214050</v>
+        <v>323200</v>
       </c>
       <c r="C808" s="0" t="s">
         <v>1564</v>
@@ -17705,27 +17720,27 @@
     </row>
     <row r="809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A809" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B809" s="0" t="s">
-        <v>4</v>
+        <v>1565</v>
+      </c>
+      <c r="B809" s="0" t="n">
+        <v>214050</v>
       </c>
       <c r="C809" s="0" t="s">
-        <v>4</v>
+        <v>1566</v>
       </c>
       <c r="D809" s="0" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="810" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A810" s="0" t="s">
-        <v>1566</v>
-      </c>
-      <c r="B810" s="0" t="n">
-        <v>341007</v>
+        <v>4</v>
+      </c>
+      <c r="B810" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C810" s="0" t="s">
-        <v>1567</v>
+        <v>4</v>
       </c>
       <c r="D810" s="0" t="s">
         <v>1567</v>
@@ -17736,7 +17751,7 @@
         <v>1568</v>
       </c>
       <c r="B811" s="0" t="n">
-        <v>224002</v>
+        <v>341007</v>
       </c>
       <c r="C811" s="0" t="s">
         <v>1569</v>
@@ -17750,24 +17765,24 @@
         <v>1570</v>
       </c>
       <c r="B812" s="0" t="n">
-        <v>344020</v>
+        <v>224002</v>
       </c>
       <c r="C812" s="0" t="s">
         <v>1571</v>
       </c>
       <c r="D812" s="0" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="813" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A813" s="0" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B813" s="0" t="n">
+        <v>344020</v>
+      </c>
+      <c r="C813" s="0" t="s">
         <v>1573</v>
-      </c>
-      <c r="B813" s="0" t="n">
-        <v>343001</v>
-      </c>
-      <c r="C813" s="0" t="s">
-        <v>1574</v>
       </c>
       <c r="D813" s="0" t="s">
         <v>1574</v>
@@ -17778,7 +17793,7 @@
         <v>1575</v>
       </c>
       <c r="B814" s="0" t="n">
-        <v>322040</v>
+        <v>343001</v>
       </c>
       <c r="C814" s="0" t="s">
         <v>1576</v>
@@ -17792,7 +17807,7 @@
         <v>1577</v>
       </c>
       <c r="B815" s="0" t="n">
-        <v>329020</v>
+        <v>322040</v>
       </c>
       <c r="C815" s="0" t="s">
         <v>1578</v>
@@ -17806,7 +17821,7 @@
         <v>1579</v>
       </c>
       <c r="B816" s="0" t="n">
-        <v>341024</v>
+        <v>329020</v>
       </c>
       <c r="C816" s="0" t="s">
         <v>1580</v>
@@ -17820,7 +17835,7 @@
         <v>1581</v>
       </c>
       <c r="B817" s="0" t="n">
-        <v>352090</v>
+        <v>341024</v>
       </c>
       <c r="C817" s="0" t="s">
         <v>1582</v>
@@ -17834,7 +17849,7 @@
         <v>1583</v>
       </c>
       <c r="B818" s="0" t="n">
-        <v>264050</v>
+        <v>352090</v>
       </c>
       <c r="C818" s="0" t="s">
         <v>1584</v>
@@ -17848,7 +17863,7 @@
         <v>1585</v>
       </c>
       <c r="B819" s="0" t="n">
-        <v>224003</v>
+        <v>264050</v>
       </c>
       <c r="C819" s="0" t="s">
         <v>1586</v>
@@ -17862,7 +17877,7 @@
         <v>1587</v>
       </c>
       <c r="B820" s="0" t="n">
-        <v>382030</v>
+        <v>224003</v>
       </c>
       <c r="C820" s="0" t="s">
         <v>1588</v>
@@ -17876,38 +17891,38 @@
         <v>1589</v>
       </c>
       <c r="B821" s="0" t="n">
-        <v>357020</v>
+        <v>382030</v>
       </c>
       <c r="C821" s="0" t="s">
         <v>1590</v>
       </c>
       <c r="D821" s="0" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="822" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A822" s="0" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B822" s="0" t="n">
+        <v>357020</v>
+      </c>
+      <c r="C822" s="0" t="s">
         <v>1592</v>
       </c>
-      <c r="B822" s="0" t="n">
-        <v>341110</v>
-      </c>
-      <c r="C822" s="0" t="s">
+      <c r="D822" s="0" t="s">
         <v>1593</v>
-      </c>
-      <c r="D822" s="0" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="823" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A823" s="0" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B823" s="0" t="n">
+        <v>341110</v>
+      </c>
+      <c r="C823" s="0" t="s">
         <v>1595</v>
-      </c>
-      <c r="B823" s="0" t="n">
-        <v>343100</v>
-      </c>
-      <c r="C823" s="0" t="s">
-        <v>1596</v>
       </c>
       <c r="D823" s="0" t="s">
         <v>1596</v>
@@ -17918,7 +17933,7 @@
         <v>1597</v>
       </c>
       <c r="B824" s="0" t="n">
-        <v>273060</v>
+        <v>343100</v>
       </c>
       <c r="C824" s="0" t="s">
         <v>1598</v>
@@ -17932,38 +17947,38 @@
         <v>1599</v>
       </c>
       <c r="B825" s="0" t="n">
-        <v>357062</v>
+        <v>273060</v>
       </c>
       <c r="C825" s="0" t="s">
         <v>1600</v>
       </c>
       <c r="D825" s="0" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="826" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A826" s="0" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B826" s="0" t="n">
+        <v>357062</v>
+      </c>
+      <c r="C826" s="0" t="s">
         <v>1602</v>
       </c>
-      <c r="B826" s="0" t="n">
-        <v>355070</v>
-      </c>
-      <c r="C826" s="0" t="s">
+      <c r="D826" s="0" t="s">
         <v>1603</v>
-      </c>
-      <c r="D826" s="0" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="827" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A827" s="0" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B827" s="0" t="n">
+        <v>355070</v>
+      </c>
+      <c r="C827" s="0" t="s">
         <v>1605</v>
-      </c>
-      <c r="B827" s="0" t="n">
-        <v>343050</v>
-      </c>
-      <c r="C827" s="0" t="s">
-        <v>1606</v>
       </c>
       <c r="D827" s="0" t="s">
         <v>1606</v>
@@ -17974,7 +17989,7 @@
         <v>1607</v>
       </c>
       <c r="B828" s="0" t="n">
-        <v>343020</v>
+        <v>343050</v>
       </c>
       <c r="C828" s="0" t="s">
         <v>1608</v>
@@ -17985,27 +18000,27 @@
     </row>
     <row r="829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A829" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B829" s="0" t="s">
-        <v>4</v>
+        <v>1609</v>
+      </c>
+      <c r="B829" s="0" t="n">
+        <v>343020</v>
       </c>
       <c r="C829" s="0" t="s">
-        <v>4</v>
+        <v>1610</v>
       </c>
       <c r="D829" s="0" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A830" s="0" t="s">
-        <v>1610</v>
-      </c>
-      <c r="B830" s="0" t="n">
-        <v>224004</v>
+        <v>4</v>
+      </c>
+      <c r="B830" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C830" s="0" t="s">
-        <v>1611</v>
+        <v>4</v>
       </c>
       <c r="D830" s="0" t="s">
         <v>1611</v>
@@ -18016,7 +18031,7 @@
         <v>1612</v>
       </c>
       <c r="B831" s="0" t="n">
-        <v>324030</v>
+        <v>224004</v>
       </c>
       <c r="C831" s="0" t="s">
         <v>1613</v>
@@ -18027,27 +18042,27 @@
     </row>
     <row r="832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A832" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B832" s="0" t="s">
-        <v>4</v>
+        <v>1614</v>
+      </c>
+      <c r="B832" s="0" t="n">
+        <v>324030</v>
       </c>
       <c r="C832" s="0" t="s">
-        <v>4</v>
+        <v>1615</v>
       </c>
       <c r="D832" s="0" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A833" s="0" t="s">
-        <v>1615</v>
-      </c>
-      <c r="B833" s="0" t="n">
-        <v>212040</v>
+        <v>4</v>
+      </c>
+      <c r="B833" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C833" s="0" t="s">
-        <v>1616</v>
+        <v>4</v>
       </c>
       <c r="D833" s="0" t="s">
         <v>1616</v>
@@ -18058,7 +18073,7 @@
         <v>1617</v>
       </c>
       <c r="B834" s="0" t="n">
-        <v>343070</v>
+        <v>212040</v>
       </c>
       <c r="C834" s="0" t="s">
         <v>1618</v>
@@ -18072,7 +18087,7 @@
         <v>1619</v>
       </c>
       <c r="B835" s="0" t="n">
-        <v>354002</v>
+        <v>343070</v>
       </c>
       <c r="C835" s="0" t="s">
         <v>1620</v>
@@ -18086,7 +18101,7 @@
         <v>1621</v>
       </c>
       <c r="B836" s="0" t="n">
-        <v>261131</v>
+        <v>354002</v>
       </c>
       <c r="C836" s="0" t="s">
         <v>1622</v>
@@ -18100,24 +18115,24 @@
         <v>1623</v>
       </c>
       <c r="B837" s="0" t="n">
-        <v>290080</v>
+        <v>261131</v>
       </c>
       <c r="C837" s="0" t="s">
         <v>1624</v>
       </c>
       <c r="D837" s="0" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A838" s="0" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B838" s="0" t="n">
+        <v>290080</v>
+      </c>
+      <c r="C838" s="0" t="s">
         <v>1626</v>
-      </c>
-      <c r="B838" s="0" t="n">
-        <v>300201</v>
-      </c>
-      <c r="C838" s="0" t="s">
-        <v>1627</v>
       </c>
       <c r="D838" s="0" t="s">
         <v>1627</v>
@@ -18128,7 +18143,7 @@
         <v>1628</v>
       </c>
       <c r="B839" s="0" t="n">
-        <v>300520</v>
+        <v>300201</v>
       </c>
       <c r="C839" s="0" t="s">
         <v>1629</v>
@@ -18142,7 +18157,7 @@
         <v>1630</v>
       </c>
       <c r="B840" s="0" t="n">
-        <v>222050</v>
+        <v>300520</v>
       </c>
       <c r="C840" s="0" t="s">
         <v>1631</v>
@@ -18156,7 +18171,7 @@
         <v>1632</v>
       </c>
       <c r="B841" s="0" t="n">
-        <v>311180</v>
+        <v>222050</v>
       </c>
       <c r="C841" s="0" t="s">
         <v>1633</v>
@@ -18170,7 +18185,7 @@
         <v>1634</v>
       </c>
       <c r="B842" s="0" t="n">
-        <v>311030</v>
+        <v>311180</v>
       </c>
       <c r="C842" s="0" t="s">
         <v>1635</v>
@@ -18184,7 +18199,7 @@
         <v>1636</v>
       </c>
       <c r="B843" s="0" t="n">
-        <v>261260</v>
+        <v>311030</v>
       </c>
       <c r="C843" s="0" t="s">
         <v>1637</v>
@@ -18198,7 +18213,7 @@
         <v>1638</v>
       </c>
       <c r="B844" s="0" t="n">
-        <v>263300</v>
+        <v>261260</v>
       </c>
       <c r="C844" s="0" t="s">
         <v>1639</v>
@@ -18212,38 +18227,38 @@
         <v>1640</v>
       </c>
       <c r="B845" s="0" t="n">
-        <v>341092</v>
+        <v>263300</v>
       </c>
       <c r="C845" s="0" t="s">
         <v>1641</v>
       </c>
       <c r="D845" s="0" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A846" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B846" s="0" t="s">
-        <v>4</v>
+        <v>1642</v>
+      </c>
+      <c r="B846" s="0" t="n">
+        <v>341092</v>
       </c>
       <c r="C846" s="0" t="s">
-        <v>4</v>
+        <v>1643</v>
       </c>
       <c r="D846" s="0" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A847" s="0" t="s">
-        <v>1644</v>
-      </c>
-      <c r="B847" s="0" t="n">
-        <v>261020</v>
+        <v>4</v>
+      </c>
+      <c r="B847" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C847" s="0" t="s">
-        <v>1645</v>
+        <v>4</v>
       </c>
       <c r="D847" s="0" t="s">
         <v>1645</v>
@@ -18254,7 +18269,7 @@
         <v>1646</v>
       </c>
       <c r="B848" s="0" t="n">
-        <v>300700</v>
+        <v>261020</v>
       </c>
       <c r="C848" s="0" t="s">
         <v>1647</v>
@@ -18268,7 +18283,7 @@
         <v>1648</v>
       </c>
       <c r="B849" s="0" t="n">
-        <v>230010</v>
+        <v>300700</v>
       </c>
       <c r="C849" s="0" t="s">
         <v>1649</v>
@@ -18282,7 +18297,7 @@
         <v>1650</v>
       </c>
       <c r="B850" s="0" t="n">
-        <v>323010</v>
+        <v>230010</v>
       </c>
       <c r="C850" s="0" t="s">
         <v>1651</v>
@@ -18296,7 +18311,7 @@
         <v>1652</v>
       </c>
       <c r="B851" s="0" t="n">
-        <v>300270</v>
+        <v>323010</v>
       </c>
       <c r="C851" s="0" t="s">
         <v>1653</v>
@@ -18307,16 +18322,16 @@
     </row>
     <row r="852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A852" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B852" s="0" t="s">
-        <v>4</v>
+        <v>1654</v>
+      </c>
+      <c r="B852" s="0" t="n">
+        <v>300270</v>
       </c>
       <c r="C852" s="0" t="s">
-        <v>4</v>
+        <v>1655</v>
       </c>
       <c r="D852" s="0" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18330,7 +18345,7 @@
         <v>4</v>
       </c>
       <c r="D853" s="0" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18344,7 +18359,7 @@
         <v>4</v>
       </c>
       <c r="D854" s="0" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18358,18 +18373,18 @@
         <v>4</v>
       </c>
       <c r="D855" s="0" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A856" s="0" t="s">
-        <v>1658</v>
-      </c>
-      <c r="B856" s="0" t="n">
-        <v>300511</v>
+        <v>4</v>
+      </c>
+      <c r="B856" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C856" s="0" t="s">
-        <v>1659</v>
+        <v>4</v>
       </c>
       <c r="D856" s="0" t="s">
         <v>1659</v>
@@ -18380,7 +18395,7 @@
         <v>1660</v>
       </c>
       <c r="B857" s="0" t="n">
-        <v>300580</v>
+        <v>300511</v>
       </c>
       <c r="C857" s="0" t="s">
         <v>1661</v>
@@ -18394,7 +18409,7 @@
         <v>1662</v>
       </c>
       <c r="B858" s="0" t="n">
-        <v>261110</v>
+        <v>300580</v>
       </c>
       <c r="C858" s="0" t="s">
         <v>1663</v>
@@ -18408,7 +18423,7 @@
         <v>1664</v>
       </c>
       <c r="B859" s="0" t="n">
-        <v>353050</v>
+        <v>261110</v>
       </c>
       <c r="C859" s="0" t="s">
         <v>1665</v>
@@ -18422,7 +18437,7 @@
         <v>1666</v>
       </c>
       <c r="B860" s="0" t="n">
-        <v>222052</v>
+        <v>353050</v>
       </c>
       <c r="C860" s="0" t="s">
         <v>1667</v>
@@ -18436,7 +18451,7 @@
         <v>1668</v>
       </c>
       <c r="B861" s="0" t="n">
-        <v>272040</v>
+        <v>222052</v>
       </c>
       <c r="C861" s="0" t="s">
         <v>1669</v>
@@ -18450,7 +18465,7 @@
         <v>1670</v>
       </c>
       <c r="B862" s="0" t="n">
-        <v>320160</v>
+        <v>272040</v>
       </c>
       <c r="C862" s="0" t="s">
         <v>1671</v>
@@ -18464,7 +18479,7 @@
         <v>1672</v>
       </c>
       <c r="B863" s="0" t="n">
-        <v>261080</v>
+        <v>320160</v>
       </c>
       <c r="C863" s="0" t="s">
         <v>1673</v>
@@ -18478,7 +18493,7 @@
         <v>1674</v>
       </c>
       <c r="B864" s="0" t="n">
-        <v>261070</v>
+        <v>261080</v>
       </c>
       <c r="C864" s="0" t="s">
         <v>1675</v>
@@ -18492,7 +18507,7 @@
         <v>1676</v>
       </c>
       <c r="B865" s="0" t="n">
-        <v>264270</v>
+        <v>261070</v>
       </c>
       <c r="C865" s="0" t="s">
         <v>1677</v>
@@ -18506,7 +18521,7 @@
         <v>1678</v>
       </c>
       <c r="B866" s="0" t="n">
-        <v>263180</v>
+        <v>264270</v>
       </c>
       <c r="C866" s="0" t="s">
         <v>1679</v>
@@ -18520,7 +18535,7 @@
         <v>1680</v>
       </c>
       <c r="B867" s="0" t="n">
-        <v>370010</v>
+        <v>263180</v>
       </c>
       <c r="C867" s="0" t="s">
         <v>1681</v>
@@ -18534,7 +18549,7 @@
         <v>1682</v>
       </c>
       <c r="B868" s="0" t="n">
-        <v>300690</v>
+        <v>370010</v>
       </c>
       <c r="C868" s="0" t="s">
         <v>1683</v>
@@ -18548,7 +18563,7 @@
         <v>1684</v>
       </c>
       <c r="B869" s="0" t="n">
-        <v>300660</v>
+        <v>300690</v>
       </c>
       <c r="C869" s="0" t="s">
         <v>1685</v>
@@ -18562,7 +18577,7 @@
         <v>1686</v>
       </c>
       <c r="B870" s="0" t="n">
-        <v>312200</v>
+        <v>300660</v>
       </c>
       <c r="C870" s="0" t="s">
         <v>1687</v>
@@ -18576,7 +18591,7 @@
         <v>1688</v>
       </c>
       <c r="B871" s="0" t="n">
-        <v>352001</v>
+        <v>312200</v>
       </c>
       <c r="C871" s="0" t="s">
         <v>1689</v>
@@ -18590,7 +18605,7 @@
         <v>1690</v>
       </c>
       <c r="B872" s="0" t="n">
-        <v>355109</v>
+        <v>352001</v>
       </c>
       <c r="C872" s="0" t="s">
         <v>1691</v>
@@ -18604,7 +18619,7 @@
         <v>1692</v>
       </c>
       <c r="B873" s="0" t="n">
-        <v>326010</v>
+        <v>355109</v>
       </c>
       <c r="C873" s="0" t="s">
         <v>1693</v>
@@ -18618,7 +18633,7 @@
         <v>1694</v>
       </c>
       <c r="B874" s="0" t="n">
-        <v>221222</v>
+        <v>326010</v>
       </c>
       <c r="C874" s="0" t="s">
         <v>1695</v>
@@ -18632,7 +18647,7 @@
         <v>1696</v>
       </c>
       <c r="B875" s="0" t="n">
-        <v>357111</v>
+        <v>221222</v>
       </c>
       <c r="C875" s="0" t="s">
         <v>1697</v>
@@ -18646,7 +18661,7 @@
         <v>1698</v>
       </c>
       <c r="B876" s="0" t="n">
-        <v>266030</v>
+        <v>357111</v>
       </c>
       <c r="C876" s="0" t="s">
         <v>1699</v>
@@ -18660,7 +18675,7 @@
         <v>1700</v>
       </c>
       <c r="B877" s="0" t="n">
-        <v>261120</v>
+        <v>266030</v>
       </c>
       <c r="C877" s="0" t="s">
         <v>1701</v>
@@ -18671,83 +18686,83 @@
     </row>
     <row r="878" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A878" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B878" s="0" t="s">
-        <v>4</v>
+        <v>1702</v>
+      </c>
+      <c r="B878" s="0" t="n">
+        <v>261120</v>
       </c>
       <c r="C878" s="0" t="s">
-        <v>4</v>
+        <v>1703</v>
       </c>
       <c r="D878" s="0" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="879" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A879" s="0" t="s">
-        <v>1703</v>
-      </c>
-      <c r="B879" s="0" t="n">
-        <v>351061</v>
+        <v>4</v>
+      </c>
+      <c r="B879" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C879" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D879" s="0" t="s">
         <v>1704</v>
-      </c>
-      <c r="D879" s="0" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="880" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A880" s="0" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B880" s="0" t="n">
+        <v>351061</v>
+      </c>
+      <c r="C880" s="0" t="s">
         <v>1706</v>
       </c>
-      <c r="B880" s="0" t="n">
-        <v>360060</v>
-      </c>
-      <c r="C880" s="0" t="s">
+      <c r="D880" s="0" t="s">
         <v>1707</v>
-      </c>
-      <c r="D880" s="0" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="881" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A881" s="0" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B881" s="0" t="n">
+        <v>360060</v>
+      </c>
+      <c r="C881" s="0" t="s">
         <v>1709</v>
       </c>
-      <c r="B881" s="0" t="n">
-        <v>360050</v>
-      </c>
-      <c r="C881" s="0" t="s">
+      <c r="D881" s="0" t="s">
         <v>1710</v>
-      </c>
-      <c r="D881" s="0" t="s">
-        <v>1711</v>
       </c>
     </row>
     <row r="882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A882" s="0" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B882" s="0" t="n">
+        <v>360050</v>
+      </c>
+      <c r="C882" s="0" t="s">
         <v>1712</v>
       </c>
-      <c r="B882" s="0" t="n">
-        <v>360150</v>
-      </c>
-      <c r="C882" s="0" t="s">
+      <c r="D882" s="0" t="s">
         <v>1713</v>
-      </c>
-      <c r="D882" s="0" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A883" s="0" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B883" s="0" t="n">
+        <v>360150</v>
+      </c>
+      <c r="C883" s="0" t="s">
         <v>1715</v>
-      </c>
-      <c r="B883" s="0" t="n">
-        <v>222020</v>
-      </c>
-      <c r="C883" s="0" t="s">
-        <v>1716</v>
       </c>
       <c r="D883" s="0" t="s">
         <v>1716</v>
@@ -18758,7 +18773,7 @@
         <v>1717</v>
       </c>
       <c r="B884" s="0" t="n">
-        <v>320070</v>
+        <v>222020</v>
       </c>
       <c r="C884" s="0" t="s">
         <v>1718</v>
@@ -18772,7 +18787,7 @@
         <v>1719</v>
       </c>
       <c r="B885" s="0" t="n">
-        <v>300671</v>
+        <v>320070</v>
       </c>
       <c r="C885" s="0" t="s">
         <v>1720</v>
@@ -18786,7 +18801,7 @@
         <v>1721</v>
       </c>
       <c r="B886" s="0" t="n">
-        <v>360170</v>
+        <v>300671</v>
       </c>
       <c r="C886" s="0" t="s">
         <v>1722</v>
@@ -18800,24 +18815,24 @@
         <v>1723</v>
       </c>
       <c r="B887" s="0" t="n">
-        <v>312220</v>
+        <v>360170</v>
       </c>
       <c r="C887" s="0" t="s">
         <v>1724</v>
       </c>
       <c r="D887" s="0" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="888" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A888" s="0" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B888" s="0" t="n">
+        <v>312220</v>
+      </c>
+      <c r="C888" s="0" t="s">
         <v>1726</v>
-      </c>
-      <c r="B888" s="0" t="n">
-        <v>321050</v>
-      </c>
-      <c r="C888" s="0" t="s">
-        <v>1727</v>
       </c>
       <c r="D888" s="0" t="s">
         <v>1727</v>
@@ -18828,7 +18843,7 @@
         <v>1728</v>
       </c>
       <c r="B889" s="0" t="n">
-        <v>211040</v>
+        <v>321050</v>
       </c>
       <c r="C889" s="0" t="s">
         <v>1729</v>
@@ -18842,24 +18857,24 @@
         <v>1730</v>
       </c>
       <c r="B890" s="0" t="n">
-        <v>342160</v>
+        <v>211040</v>
       </c>
       <c r="C890" s="0" t="s">
         <v>1731</v>
       </c>
       <c r="D890" s="0" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A891" s="0" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B891" s="0" t="n">
+        <v>342160</v>
+      </c>
+      <c r="C891" s="0" t="s">
         <v>1733</v>
-      </c>
-      <c r="B891" s="0" t="n">
-        <v>264120</v>
-      </c>
-      <c r="C891" s="0" t="s">
-        <v>1734</v>
       </c>
       <c r="D891" s="0" t="s">
         <v>1734</v>
@@ -18867,27 +18882,27 @@
     </row>
     <row r="892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A892" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B892" s="0" t="s">
-        <v>4</v>
+        <v>1735</v>
+      </c>
+      <c r="B892" s="0" t="n">
+        <v>264120</v>
       </c>
       <c r="C892" s="0" t="s">
-        <v>4</v>
+        <v>1736</v>
       </c>
       <c r="D892" s="0" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A893" s="0" t="s">
-        <v>1736</v>
-      </c>
-      <c r="B893" s="0" t="n">
-        <v>352040</v>
+        <v>4</v>
+      </c>
+      <c r="B893" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C893" s="0" t="s">
-        <v>1737</v>
+        <v>4</v>
       </c>
       <c r="D893" s="0" t="s">
         <v>1737</v>
@@ -18898,7 +18913,7 @@
         <v>1738</v>
       </c>
       <c r="B894" s="0" t="n">
-        <v>261180</v>
+        <v>352040</v>
       </c>
       <c r="C894" s="0" t="s">
         <v>1739</v>
@@ -18912,7 +18927,7 @@
         <v>1740</v>
       </c>
       <c r="B895" s="0" t="n">
-        <v>263210</v>
+        <v>261180</v>
       </c>
       <c r="C895" s="0" t="s">
         <v>1741</v>
@@ -18926,7 +18941,7 @@
         <v>1742</v>
       </c>
       <c r="B896" s="0" t="n">
-        <v>261270</v>
+        <v>263210</v>
       </c>
       <c r="C896" s="0" t="s">
         <v>1743</v>
@@ -18940,7 +18955,7 @@
         <v>1744</v>
       </c>
       <c r="B897" s="0" t="n">
-        <v>222110</v>
+        <v>261270</v>
       </c>
       <c r="C897" s="0" t="s">
         <v>1745</v>
@@ -18951,27 +18966,27 @@
     </row>
     <row r="898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A898" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B898" s="0" t="s">
-        <v>4</v>
+        <v>1746</v>
+      </c>
+      <c r="B898" s="0" t="n">
+        <v>222110</v>
       </c>
       <c r="C898" s="0" t="s">
-        <v>4</v>
+        <v>1747</v>
       </c>
       <c r="D898" s="0" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A899" s="0" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B899" s="0" t="n">
-        <v>273070</v>
+        <v>4</v>
+      </c>
+      <c r="B899" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C899" s="0" t="s">
-        <v>1748</v>
+        <v>4</v>
       </c>
       <c r="D899" s="0" t="s">
         <v>1748</v>
@@ -18982,7 +18997,7 @@
         <v>1749</v>
       </c>
       <c r="B900" s="0" t="n">
-        <v>355011</v>
+        <v>273070</v>
       </c>
       <c r="C900" s="0" t="s">
         <v>1750</v>
@@ -18996,7 +19011,7 @@
         <v>1751</v>
       </c>
       <c r="B901" s="0" t="n">
-        <v>343072</v>
+        <v>355011</v>
       </c>
       <c r="C901" s="0" t="s">
         <v>1752</v>
@@ -19010,24 +19025,24 @@
         <v>1753</v>
       </c>
       <c r="B902" s="0" t="n">
-        <v>341130</v>
+        <v>343072</v>
       </c>
       <c r="C902" s="0" t="s">
         <v>1754</v>
       </c>
       <c r="D902" s="0" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="903" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A903" s="0" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B903" s="0" t="n">
+        <v>341130</v>
+      </c>
+      <c r="C903" s="0" t="s">
         <v>1756</v>
-      </c>
-      <c r="B903" s="0" t="n">
-        <v>355010</v>
-      </c>
-      <c r="C903" s="0" t="s">
-        <v>1757</v>
       </c>
       <c r="D903" s="0" t="s">
         <v>1757</v>
@@ -19038,7 +19053,7 @@
         <v>1758</v>
       </c>
       <c r="B904" s="0" t="n">
-        <v>232050</v>
+        <v>355010</v>
       </c>
       <c r="C904" s="0" t="s">
         <v>1759</v>
@@ -19052,7 +19067,7 @@
         <v>1760</v>
       </c>
       <c r="B905" s="0" t="n">
-        <v>225004</v>
+        <v>232050</v>
       </c>
       <c r="C905" s="0" t="s">
         <v>1761</v>
@@ -19066,7 +19081,7 @@
         <v>1762</v>
       </c>
       <c r="B906" s="0" t="n">
-        <v>342141</v>
+        <v>225004</v>
       </c>
       <c r="C906" s="0" t="s">
         <v>1763</v>
@@ -19077,27 +19092,27 @@
     </row>
     <row r="907" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A907" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B907" s="0" t="s">
-        <v>4</v>
+        <v>1764</v>
+      </c>
+      <c r="B907" s="0" t="n">
+        <v>342141</v>
       </c>
       <c r="C907" s="0" t="s">
-        <v>4</v>
+        <v>1765</v>
       </c>
       <c r="D907" s="0" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A908" s="0" t="s">
-        <v>1765</v>
-      </c>
-      <c r="B908" s="0" t="n">
-        <v>342020</v>
+        <v>4</v>
+      </c>
+      <c r="B908" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C908" s="0" t="s">
-        <v>1766</v>
+        <v>4</v>
       </c>
       <c r="D908" s="0" t="s">
         <v>1766</v>
@@ -19105,27 +19120,27 @@
     </row>
     <row r="909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A909" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B909" s="0" t="s">
-        <v>4</v>
+        <v>1767</v>
+      </c>
+      <c r="B909" s="0" t="n">
+        <v>342020</v>
       </c>
       <c r="C909" s="0" t="s">
-        <v>4</v>
+        <v>1768</v>
       </c>
       <c r="D909" s="0" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A910" s="0" t="s">
-        <v>1768</v>
-      </c>
-      <c r="B910" s="0" t="n">
-        <v>311090</v>
+        <v>4</v>
+      </c>
+      <c r="B910" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C910" s="0" t="s">
-        <v>1769</v>
+        <v>4</v>
       </c>
       <c r="D910" s="0" t="s">
         <v>1769</v>
@@ -19133,27 +19148,27 @@
     </row>
     <row r="911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A911" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B911" s="0" t="s">
-        <v>4</v>
+        <v>1770</v>
+      </c>
+      <c r="B911" s="0" t="n">
+        <v>311090</v>
       </c>
       <c r="C911" s="0" t="s">
-        <v>4</v>
+        <v>1771</v>
       </c>
       <c r="D911" s="0" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A912" s="0" t="s">
-        <v>1771</v>
-      </c>
-      <c r="B912" s="0" t="n">
-        <v>263150</v>
+        <v>4</v>
+      </c>
+      <c r="B912" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C912" s="0" t="s">
-        <v>1772</v>
+        <v>4</v>
       </c>
       <c r="D912" s="0" t="s">
         <v>1772</v>
@@ -19164,7 +19179,7 @@
         <v>1773</v>
       </c>
       <c r="B913" s="0" t="n">
-        <v>261130</v>
+        <v>263150</v>
       </c>
       <c r="C913" s="0" t="s">
         <v>1774</v>
@@ -19178,7 +19193,7 @@
         <v>1775</v>
       </c>
       <c r="B914" s="0" t="n">
-        <v>261160</v>
+        <v>261130</v>
       </c>
       <c r="C914" s="0" t="s">
         <v>1776</v>
@@ -19192,7 +19207,7 @@
         <v>1777</v>
       </c>
       <c r="B915" s="0" t="n">
-        <v>355021</v>
+        <v>261160</v>
       </c>
       <c r="C915" s="0" t="s">
         <v>1778</v>
@@ -19206,7 +19221,7 @@
         <v>1779</v>
       </c>
       <c r="B916" s="0" t="n">
-        <v>264040</v>
+        <v>355021</v>
       </c>
       <c r="C916" s="0" t="s">
         <v>1780</v>
@@ -19220,7 +19235,7 @@
         <v>1781</v>
       </c>
       <c r="B917" s="0" t="n">
-        <v>263131</v>
+        <v>264040</v>
       </c>
       <c r="C917" s="0" t="s">
         <v>1782</v>
@@ -19234,7 +19249,7 @@
         <v>1783</v>
       </c>
       <c r="B918" s="0" t="n">
-        <v>311241</v>
+        <v>263131</v>
       </c>
       <c r="C918" s="0" t="s">
         <v>1784</v>
@@ -19248,7 +19263,7 @@
         <v>1785</v>
       </c>
       <c r="B919" s="0" t="n">
-        <v>311080</v>
+        <v>311241</v>
       </c>
       <c r="C919" s="0" t="s">
         <v>1786</v>
@@ -19262,7 +19277,7 @@
         <v>1787</v>
       </c>
       <c r="B920" s="0" t="n">
-        <v>261150</v>
+        <v>311080</v>
       </c>
       <c r="C920" s="0" t="s">
         <v>1788</v>
@@ -19276,7 +19291,7 @@
         <v>1789</v>
       </c>
       <c r="B921" s="0" t="n">
-        <v>266130</v>
+        <v>261150</v>
       </c>
       <c r="C921" s="0" t="s">
         <v>1790</v>
@@ -19290,7 +19305,7 @@
         <v>1791</v>
       </c>
       <c r="B922" s="0" t="n">
-        <v>263090</v>
+        <v>266130</v>
       </c>
       <c r="C922" s="0" t="s">
         <v>1792</v>
@@ -19304,7 +19319,7 @@
         <v>1793</v>
       </c>
       <c r="B923" s="0" t="n">
-        <v>268001</v>
+        <v>263090</v>
       </c>
       <c r="C923" s="0" t="s">
         <v>1794</v>
@@ -19318,24 +19333,24 @@
         <v>1795</v>
       </c>
       <c r="B924" s="0" t="n">
-        <v>241030</v>
+        <v>268001</v>
       </c>
       <c r="C924" s="0" t="s">
         <v>1796</v>
       </c>
       <c r="D924" s="0" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A925" s="0" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B925" s="0" t="n">
+        <v>241030</v>
+      </c>
+      <c r="C925" s="0" t="s">
         <v>1798</v>
-      </c>
-      <c r="B925" s="0" t="n">
-        <v>225009</v>
-      </c>
-      <c r="C925" s="0" t="s">
-        <v>1799</v>
       </c>
       <c r="D925" s="0" t="s">
         <v>1799</v>
@@ -19346,7 +19361,7 @@
         <v>1800</v>
       </c>
       <c r="B926" s="0" t="n">
-        <v>225010</v>
+        <v>225009</v>
       </c>
       <c r="C926" s="0" t="s">
         <v>1801</v>
@@ -19360,7 +19375,7 @@
         <v>1802</v>
       </c>
       <c r="B927" s="0" t="n">
-        <v>225020</v>
+        <v>225010</v>
       </c>
       <c r="C927" s="0" t="s">
         <v>1803</v>
@@ -19374,7 +19389,7 @@
         <v>1804</v>
       </c>
       <c r="B928" s="0" t="n">
-        <v>303010</v>
+        <v>225020</v>
       </c>
       <c r="C928" s="0" t="s">
         <v>1805</v>
@@ -19388,7 +19403,7 @@
         <v>1806</v>
       </c>
       <c r="B929" s="0" t="n">
-        <v>221106</v>
+        <v>303010</v>
       </c>
       <c r="C929" s="0" t="s">
         <v>1807</v>
@@ -19402,7 +19417,7 @@
         <v>1808</v>
       </c>
       <c r="B930" s="0" t="n">
-        <v>355032</v>
+        <v>221106</v>
       </c>
       <c r="C930" s="0" t="s">
         <v>1809</v>
@@ -19416,7 +19431,7 @@
         <v>1810</v>
       </c>
       <c r="B931" s="0" t="n">
-        <v>300160</v>
+        <v>355032</v>
       </c>
       <c r="C931" s="0" t="s">
         <v>1811</v>
@@ -19430,7 +19445,7 @@
         <v>1812</v>
       </c>
       <c r="B932" s="0" t="n">
-        <v>241070</v>
+        <v>300160</v>
       </c>
       <c r="C932" s="0" t="s">
         <v>1813</v>
@@ -19441,27 +19456,27 @@
     </row>
     <row r="933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A933" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B933" s="0" t="s">
-        <v>4</v>
+        <v>1814</v>
+      </c>
+      <c r="B933" s="0" t="n">
+        <v>241070</v>
       </c>
       <c r="C933" s="0" t="s">
-        <v>4</v>
+        <v>1815</v>
       </c>
       <c r="D933" s="0" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A934" s="0" t="s">
-        <v>1815</v>
-      </c>
-      <c r="B934" s="0" t="n">
-        <v>343080</v>
+        <v>4</v>
+      </c>
+      <c r="B934" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C934" s="0" t="s">
-        <v>1816</v>
+        <v>4</v>
       </c>
       <c r="D934" s="0" t="s">
         <v>1816</v>
@@ -19472,7 +19487,7 @@
         <v>1817</v>
       </c>
       <c r="B935" s="0" t="n">
-        <v>342120</v>
+        <v>343080</v>
       </c>
       <c r="C935" s="0" t="s">
         <v>1818</v>
@@ -19486,7 +19501,7 @@
         <v>1819</v>
       </c>
       <c r="B936" s="0" t="n">
-        <v>344040</v>
+        <v>342120</v>
       </c>
       <c r="C936" s="0" t="s">
         <v>1820</v>
@@ -19500,7 +19515,7 @@
         <v>1821</v>
       </c>
       <c r="B937" s="0" t="n">
-        <v>263231</v>
+        <v>344040</v>
       </c>
       <c r="C937" s="0" t="s">
         <v>1822</v>
@@ -19511,27 +19526,27 @@
     </row>
     <row r="938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A938" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B938" s="0" t="s">
-        <v>4</v>
+        <v>1823</v>
+      </c>
+      <c r="B938" s="0" t="n">
+        <v>263231</v>
       </c>
       <c r="C938" s="0" t="s">
-        <v>4</v>
+        <v>1824</v>
       </c>
       <c r="D938" s="0" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A939" s="0" t="s">
-        <v>1824</v>
-      </c>
-      <c r="B939" s="0" t="n">
-        <v>213030</v>
+        <v>4</v>
+      </c>
+      <c r="B939" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C939" s="0" t="s">
-        <v>1825</v>
+        <v>4</v>
       </c>
       <c r="D939" s="0" t="s">
         <v>1825</v>
@@ -19542,7 +19557,7 @@
         <v>1826</v>
       </c>
       <c r="B940" s="0" t="n">
-        <v>383030</v>
+        <v>213030</v>
       </c>
       <c r="C940" s="0" t="s">
         <v>1827</v>
@@ -19556,7 +19571,7 @@
         <v>1828</v>
       </c>
       <c r="B941" s="0" t="n">
-        <v>263310</v>
+        <v>383030</v>
       </c>
       <c r="C941" s="0" t="s">
         <v>1829</v>
@@ -19570,7 +19585,7 @@
         <v>1830</v>
       </c>
       <c r="B942" s="0" t="n">
-        <v>345031</v>
+        <v>263310</v>
       </c>
       <c r="C942" s="0" t="s">
         <v>1831</v>
@@ -19584,7 +19599,7 @@
         <v>1832</v>
       </c>
       <c r="B943" s="0" t="n">
-        <v>221292</v>
+        <v>345031</v>
       </c>
       <c r="C943" s="0" t="s">
         <v>1833</v>
@@ -19598,7 +19613,7 @@
         <v>1834</v>
       </c>
       <c r="B944" s="0" t="n">
-        <v>382050</v>
+        <v>221292</v>
       </c>
       <c r="C944" s="0" t="s">
         <v>1835</v>
@@ -19612,7 +19627,7 @@
         <v>1836</v>
       </c>
       <c r="B945" s="0" t="n">
-        <v>300512</v>
+        <v>382050</v>
       </c>
       <c r="C945" s="0" t="s">
         <v>1837</v>
@@ -19626,7 +19641,7 @@
         <v>1838</v>
       </c>
       <c r="B946" s="0" t="n">
-        <v>222030</v>
+        <v>300512</v>
       </c>
       <c r="C946" s="0" t="s">
         <v>1839</v>
@@ -19637,27 +19652,27 @@
     </row>
     <row r="947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A947" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B947" s="0" t="s">
-        <v>4</v>
+        <v>1840</v>
+      </c>
+      <c r="B947" s="0" t="n">
+        <v>222030</v>
       </c>
       <c r="C947" s="0" t="s">
-        <v>4</v>
+        <v>1841</v>
       </c>
       <c r="D947" s="0" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A948" s="0" t="s">
-        <v>1841</v>
-      </c>
-      <c r="B948" s="0" t="n">
-        <v>322070</v>
+        <v>4</v>
+      </c>
+      <c r="B948" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C948" s="0" t="s">
-        <v>1842</v>
+        <v>4</v>
       </c>
       <c r="D948" s="0" t="s">
         <v>1842</v>
@@ -19668,7 +19683,7 @@
         <v>1843</v>
       </c>
       <c r="B949" s="0" t="n">
-        <v>354031</v>
+        <v>322070</v>
       </c>
       <c r="C949" s="0" t="s">
         <v>1844</v>
@@ -19682,7 +19697,7 @@
         <v>1845</v>
       </c>
       <c r="B950" s="0" t="n">
-        <v>268061</v>
+        <v>354031</v>
       </c>
       <c r="C950" s="0" t="s">
         <v>1846</v>
@@ -19696,7 +19711,7 @@
         <v>1847</v>
       </c>
       <c r="B951" s="0" t="n">
-        <v>268071</v>
+        <v>268061</v>
       </c>
       <c r="C951" s="0" t="s">
         <v>1848</v>
@@ -19710,7 +19725,7 @@
         <v>1849</v>
       </c>
       <c r="B952" s="0" t="n">
-        <v>355105</v>
+        <v>268071</v>
       </c>
       <c r="C952" s="0" t="s">
         <v>1850</v>
@@ -19724,7 +19739,7 @@
         <v>1851</v>
       </c>
       <c r="B953" s="0" t="n">
-        <v>372040</v>
+        <v>355105</v>
       </c>
       <c r="C953" s="0" t="s">
         <v>1852</v>
@@ -19738,7 +19753,7 @@
         <v>1853</v>
       </c>
       <c r="B954" s="0" t="n">
-        <v>357030</v>
+        <v>372040</v>
       </c>
       <c r="C954" s="0" t="s">
         <v>1854</v>
@@ -19752,7 +19767,7 @@
         <v>1855</v>
       </c>
       <c r="B955" s="0" t="n">
-        <v>225002</v>
+        <v>357030</v>
       </c>
       <c r="C955" s="0" t="s">
         <v>1856</v>
@@ -19766,7 +19781,7 @@
         <v>1857</v>
       </c>
       <c r="B956" s="0" t="n">
-        <v>355220</v>
+        <v>225002</v>
       </c>
       <c r="C956" s="0" t="s">
         <v>1858</v>
@@ -19780,7 +19795,7 @@
         <v>1859</v>
       </c>
       <c r="B957" s="0" t="n">
-        <v>300560</v>
+        <v>355220</v>
       </c>
       <c r="C957" s="0" t="s">
         <v>1860</v>
@@ -19794,7 +19809,7 @@
         <v>1861</v>
       </c>
       <c r="B958" s="0" t="n">
-        <v>315060</v>
+        <v>300560</v>
       </c>
       <c r="C958" s="0" t="s">
         <v>1862</v>
@@ -19808,7 +19823,7 @@
         <v>1863</v>
       </c>
       <c r="B959" s="0" t="n">
-        <v>261090</v>
+        <v>315060</v>
       </c>
       <c r="C959" s="0" t="s">
         <v>1864</v>
@@ -19822,7 +19837,7 @@
         <v>1865</v>
       </c>
       <c r="B960" s="0" t="n">
-        <v>268020</v>
+        <v>261090</v>
       </c>
       <c r="C960" s="0" t="s">
         <v>1866</v>
@@ -19836,7 +19851,7 @@
         <v>1867</v>
       </c>
       <c r="B961" s="0" t="n">
-        <v>268050</v>
+        <v>268020</v>
       </c>
       <c r="C961" s="0" t="s">
         <v>1868</v>
@@ -19847,27 +19862,27 @@
     </row>
     <row r="962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A962" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B962" s="0" t="s">
-        <v>4</v>
+        <v>1869</v>
+      </c>
+      <c r="B962" s="0" t="n">
+        <v>268050</v>
       </c>
       <c r="C962" s="0" t="s">
-        <v>4</v>
+        <v>1870</v>
       </c>
       <c r="D962" s="0" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A963" s="0" t="s">
-        <v>1870</v>
-      </c>
-      <c r="B963" s="0" t="n">
-        <v>300240</v>
+        <v>4</v>
+      </c>
+      <c r="B963" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C963" s="0" t="s">
-        <v>1871</v>
+        <v>4</v>
       </c>
       <c r="D963" s="0" t="s">
         <v>1871</v>
@@ -19878,7 +19893,7 @@
         <v>1872</v>
       </c>
       <c r="B964" s="0" t="n">
-        <v>243060</v>
+        <v>300240</v>
       </c>
       <c r="C964" s="0" t="s">
         <v>1873</v>
@@ -19892,7 +19907,7 @@
         <v>1874</v>
       </c>
       <c r="B965" s="0" t="n">
-        <v>357093</v>
+        <v>243060</v>
       </c>
       <c r="C965" s="0" t="s">
         <v>1875</v>
@@ -19906,24 +19921,24 @@
         <v>1876</v>
       </c>
       <c r="B966" s="0" t="n">
-        <v>342070</v>
+        <v>357093</v>
       </c>
       <c r="C966" s="0" t="s">
         <v>1877</v>
       </c>
       <c r="D966" s="0" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A967" s="0" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B967" s="0" t="n">
+        <v>342070</v>
+      </c>
+      <c r="C967" s="0" t="s">
         <v>1879</v>
-      </c>
-      <c r="B967" s="0" t="n">
-        <v>300082</v>
-      </c>
-      <c r="C967" s="0" t="s">
-        <v>1880</v>
       </c>
       <c r="D967" s="0" t="s">
         <v>1880</v>
@@ -19934,38 +19949,38 @@
         <v>1881</v>
       </c>
       <c r="B968" s="0" t="n">
-        <v>2900010</v>
+        <v>300082</v>
       </c>
       <c r="C968" s="0" t="s">
         <v>1882</v>
       </c>
       <c r="D968" s="0" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A969" s="0" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B969" s="0" t="n">
+        <v>2900010</v>
+      </c>
+      <c r="C969" s="0" t="s">
         <v>1884</v>
       </c>
-      <c r="B969" s="0" t="n">
-        <v>266070</v>
-      </c>
-      <c r="C969" s="0" t="s">
+      <c r="D969" s="0" t="s">
         <v>1885</v>
-      </c>
-      <c r="D969" s="0" t="s">
-        <v>1886</v>
       </c>
     </row>
     <row r="970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A970" s="0" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B970" s="0" t="n">
+        <v>266070</v>
+      </c>
+      <c r="C970" s="0" t="s">
         <v>1887</v>
-      </c>
-      <c r="B970" s="0" t="n">
-        <v>241080</v>
-      </c>
-      <c r="C970" s="0" t="s">
-        <v>1888</v>
       </c>
       <c r="D970" s="0" t="s">
         <v>1888</v>
@@ -19973,27 +19988,27 @@
     </row>
     <row r="971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A971" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B971" s="0" t="s">
-        <v>4</v>
+        <v>1889</v>
+      </c>
+      <c r="B971" s="0" t="n">
+        <v>241080</v>
       </c>
       <c r="C971" s="0" t="s">
-        <v>4</v>
+        <v>1890</v>
       </c>
       <c r="D971" s="0" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A972" s="0" t="s">
-        <v>1890</v>
-      </c>
-      <c r="B972" s="0" t="n">
-        <v>372050</v>
+        <v>4</v>
+      </c>
+      <c r="B972" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C972" s="0" t="s">
-        <v>1891</v>
+        <v>4</v>
       </c>
       <c r="D972" s="0" t="s">
         <v>1891</v>
@@ -20004,7 +20019,7 @@
         <v>1892</v>
       </c>
       <c r="B973" s="0" t="n">
-        <v>275030</v>
+        <v>372050</v>
       </c>
       <c r="C973" s="0" t="s">
         <v>1893</v>
@@ -20018,7 +20033,7 @@
         <v>1894</v>
       </c>
       <c r="B974" s="0" t="n">
-        <v>221310</v>
+        <v>275030</v>
       </c>
       <c r="C974" s="0" t="s">
         <v>1895</v>
@@ -20029,16 +20044,16 @@
     </row>
     <row r="975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A975" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B975" s="0" t="s">
-        <v>4</v>
+        <v>1896</v>
+      </c>
+      <c r="B975" s="0" t="n">
+        <v>221310</v>
       </c>
       <c r="C975" s="0" t="s">
-        <v>4</v>
+        <v>1897</v>
       </c>
       <c r="D975" s="0" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20052,7 +20067,7 @@
         <v>4</v>
       </c>
       <c r="D976" s="0" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20066,7 +20081,7 @@
         <v>4</v>
       </c>
       <c r="D977" s="0" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20080,18 +20095,18 @@
         <v>4</v>
       </c>
       <c r="D978" s="0" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A979" s="0" t="s">
-        <v>1900</v>
-      </c>
-      <c r="B979" s="0" t="n">
-        <v>357101</v>
+        <v>4</v>
+      </c>
+      <c r="B979" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C979" s="0" t="s">
-        <v>1901</v>
+        <v>4</v>
       </c>
       <c r="D979" s="0" t="s">
         <v>1901</v>
@@ -20102,24 +20117,24 @@
         <v>1902</v>
       </c>
       <c r="B980" s="0" t="n">
-        <v>341010</v>
+        <v>357101</v>
       </c>
       <c r="C980" s="0" t="s">
         <v>1903</v>
       </c>
       <c r="D980" s="0" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A981" s="0" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B981" s="0" t="n">
+        <v>341010</v>
+      </c>
+      <c r="C981" s="0" t="s">
         <v>1905</v>
-      </c>
-      <c r="B981" s="0" t="n">
-        <v>-16312160</v>
-      </c>
-      <c r="C981" s="0" t="s">
-        <v>1906</v>
       </c>
       <c r="D981" s="0" t="s">
         <v>1906</v>
@@ -20130,7 +20145,7 @@
         <v>1907</v>
       </c>
       <c r="B982" s="0" t="n">
-        <v>290113</v>
+        <v>-16312160</v>
       </c>
       <c r="C982" s="0" t="s">
         <v>1908</v>
@@ -20144,7 +20159,7 @@
         <v>1909</v>
       </c>
       <c r="B983" s="0" t="n">
-        <v>357081</v>
+        <v>290113</v>
       </c>
       <c r="C983" s="0" t="s">
         <v>1910</v>
@@ -20158,7 +20173,7 @@
         <v>1911</v>
       </c>
       <c r="B984" s="0" t="n">
-        <v>357072</v>
+        <v>357081</v>
       </c>
       <c r="C984" s="0" t="s">
         <v>1912</v>
@@ -20172,7 +20187,7 @@
         <v>1913</v>
       </c>
       <c r="B985" s="0" t="n">
-        <v>358011</v>
+        <v>357072</v>
       </c>
       <c r="C985" s="0" t="s">
         <v>1914</v>
@@ -20186,7 +20201,7 @@
         <v>1915</v>
       </c>
       <c r="B986" s="0" t="n">
-        <v>320100</v>
+        <v>358011</v>
       </c>
       <c r="C986" s="0" t="s">
         <v>1916</v>
@@ -20200,7 +20215,7 @@
         <v>1917</v>
       </c>
       <c r="B987" s="0" t="n">
-        <v>223080</v>
+        <v>320100</v>
       </c>
       <c r="C987" s="0" t="s">
         <v>1918</v>
@@ -20214,24 +20229,24 @@
         <v>1919</v>
       </c>
       <c r="B988" s="0" t="n">
-        <v>214100</v>
+        <v>223080</v>
       </c>
       <c r="C988" s="0" t="s">
         <v>1920</v>
       </c>
       <c r="D988" s="0" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A989" s="0" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B989" s="0" t="n">
+        <v>214100</v>
+      </c>
+      <c r="C989" s="0" t="s">
         <v>1922</v>
-      </c>
-      <c r="B989" s="0" t="n">
-        <v>221250</v>
-      </c>
-      <c r="C989" s="0" t="s">
-        <v>1923</v>
       </c>
       <c r="D989" s="0" t="s">
         <v>1923</v>
@@ -20242,7 +20257,7 @@
         <v>1924</v>
       </c>
       <c r="B990" s="0" t="n">
-        <v>373040</v>
+        <v>221250</v>
       </c>
       <c r="C990" s="0" t="s">
         <v>1925</v>
@@ -20256,7 +20271,7 @@
         <v>1926</v>
       </c>
       <c r="B991" s="0" t="n">
-        <v>352080</v>
+        <v>373040</v>
       </c>
       <c r="C991" s="0" t="s">
         <v>1927</v>
@@ -20270,7 +20285,7 @@
         <v>1928</v>
       </c>
       <c r="B992" s="0" t="n">
-        <v>302050</v>
+        <v>352080</v>
       </c>
       <c r="C992" s="0" t="s">
         <v>1929</v>
@@ -20284,7 +20299,7 @@
         <v>1930</v>
       </c>
       <c r="B993" s="0" t="n">
-        <v>357010</v>
+        <v>302050</v>
       </c>
       <c r="C993" s="0" t="s">
         <v>1931</v>
@@ -20298,7 +20313,7 @@
         <v>1932</v>
       </c>
       <c r="B994" s="0" t="n">
-        <v>345070</v>
+        <v>357010</v>
       </c>
       <c r="C994" s="0" t="s">
         <v>1933</v>
@@ -20312,7 +20327,7 @@
         <v>1934</v>
       </c>
       <c r="B995" s="0" t="n">
-        <v>354040</v>
+        <v>345070</v>
       </c>
       <c r="C995" s="0" t="s">
         <v>1935</v>
@@ -20326,7 +20341,7 @@
         <v>1936</v>
       </c>
       <c r="B996" s="0" t="n">
-        <v>320031</v>
+        <v>354040</v>
       </c>
       <c r="C996" s="0" t="s">
         <v>1937</v>
@@ -20340,7 +20355,7 @@
         <v>1938</v>
       </c>
       <c r="B997" s="0" t="n">
-        <v>355150</v>
+        <v>320031</v>
       </c>
       <c r="C997" s="0" t="s">
         <v>1939</v>
@@ -20354,7 +20369,7 @@
         <v>1940</v>
       </c>
       <c r="B998" s="0" t="n">
-        <v>300540</v>
+        <v>355150</v>
       </c>
       <c r="C998" s="0" t="s">
         <v>1941</v>
@@ -20368,7 +20383,7 @@
         <v>1942</v>
       </c>
       <c r="B999" s="0" t="n">
-        <v>323160</v>
+        <v>300540</v>
       </c>
       <c r="C999" s="0" t="s">
         <v>1943</v>
@@ -20382,7 +20397,7 @@
         <v>1944</v>
       </c>
       <c r="B1000" s="0" t="n">
-        <v>354020</v>
+        <v>323160</v>
       </c>
       <c r="C1000" s="0" t="s">
         <v>1945</v>
@@ -20396,7 +20411,7 @@
         <v>1946</v>
       </c>
       <c r="B1001" s="0" t="n">
-        <v>300241</v>
+        <v>354020</v>
       </c>
       <c r="C1001" s="0" t="s">
         <v>1947</v>
@@ -20410,7 +20425,7 @@
         <v>1948</v>
       </c>
       <c r="B1002" s="0" t="n">
-        <v>302030</v>
+        <v>300241</v>
       </c>
       <c r="C1002" s="0" t="s">
         <v>1949</v>
@@ -20424,7 +20439,7 @@
         <v>1950</v>
       </c>
       <c r="B1003" s="0" t="n">
-        <v>312130</v>
+        <v>302030</v>
       </c>
       <c r="C1003" s="0" t="s">
         <v>1951</v>
@@ -20438,7 +20453,7 @@
         <v>1952</v>
       </c>
       <c r="B1004" s="0" t="n">
-        <v>329010</v>
+        <v>312130</v>
       </c>
       <c r="C1004" s="0" t="s">
         <v>1953</v>
@@ -20452,7 +20467,7 @@
         <v>1954</v>
       </c>
       <c r="B1005" s="0" t="n">
-        <v>300610</v>
+        <v>329010</v>
       </c>
       <c r="C1005" s="0" t="s">
         <v>1955</v>
@@ -20466,7 +20481,7 @@
         <v>1956</v>
       </c>
       <c r="B1006" s="0" t="n">
-        <v>312131</v>
+        <v>300610</v>
       </c>
       <c r="C1006" s="0" t="s">
         <v>1957</v>
@@ -20480,7 +20495,7 @@
         <v>1958</v>
       </c>
       <c r="B1007" s="0" t="n">
-        <v>300350</v>
+        <v>312131</v>
       </c>
       <c r="C1007" s="0" t="s">
         <v>1959</v>
@@ -20494,7 +20509,7 @@
         <v>1960</v>
       </c>
       <c r="B1008" s="0" t="n">
-        <v>252120</v>
+        <v>300350</v>
       </c>
       <c r="C1008" s="0" t="s">
         <v>1961</v>
@@ -20508,7 +20523,7 @@
         <v>1962</v>
       </c>
       <c r="B1009" s="0" t="n">
-        <v>311250</v>
+        <v>252120</v>
       </c>
       <c r="C1009" s="0" t="s">
         <v>1963</v>
@@ -20522,7 +20537,7 @@
         <v>1964</v>
       </c>
       <c r="B1010" s="0" t="n">
-        <v>306030</v>
+        <v>311250</v>
       </c>
       <c r="C1010" s="0" t="s">
         <v>1965</v>
@@ -20533,27 +20548,27 @@
     </row>
     <row r="1011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1011" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1011" s="0" t="s">
-        <v>4</v>
+        <v>1966</v>
+      </c>
+      <c r="B1011" s="0" t="n">
+        <v>306030</v>
       </c>
       <c r="C1011" s="0" t="s">
-        <v>4</v>
+        <v>1967</v>
       </c>
       <c r="D1011" s="0" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1012" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1012" s="0" t="s">
-        <v>1967</v>
-      </c>
-      <c r="B1012" s="0" t="n">
-        <v>263230</v>
+        <v>4</v>
+      </c>
+      <c r="B1012" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1012" s="0" t="s">
-        <v>1968</v>
+        <v>4</v>
       </c>
       <c r="D1012" s="0" t="s">
         <v>1968</v>
@@ -20561,27 +20576,27 @@
     </row>
     <row r="1013" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1013" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1013" s="0" t="s">
-        <v>4</v>
+        <v>1969</v>
+      </c>
+      <c r="B1013" s="0" t="n">
+        <v>263230</v>
       </c>
       <c r="C1013" s="0" t="s">
-        <v>4</v>
+        <v>1970</v>
       </c>
       <c r="D1013" s="0" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1014" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1014" s="0" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B1014" s="0" t="n">
-        <v>290191</v>
+        <v>4</v>
+      </c>
+      <c r="B1014" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1014" s="0" t="s">
-        <v>1971</v>
+        <v>4</v>
       </c>
       <c r="D1014" s="0" t="s">
         <v>1971</v>
@@ -20592,7 +20607,7 @@
         <v>1972</v>
       </c>
       <c r="B1015" s="0" t="n">
-        <v>300261</v>
+        <v>290191</v>
       </c>
       <c r="C1015" s="0" t="s">
         <v>1973</v>
@@ -20606,24 +20621,24 @@
         <v>1974</v>
       </c>
       <c r="B1016" s="0" t="n">
-        <v>343081</v>
+        <v>300261</v>
       </c>
       <c r="C1016" s="0" t="s">
         <v>1975</v>
       </c>
       <c r="D1016" s="0" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1017" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1017" s="0" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B1017" s="0" t="n">
+        <v>343081</v>
+      </c>
+      <c r="C1017" s="0" t="s">
         <v>1977</v>
-      </c>
-      <c r="B1017" s="0" t="n">
-        <v>355838</v>
-      </c>
-      <c r="C1017" s="0" t="s">
-        <v>1978</v>
       </c>
       <c r="D1017" s="0" t="s">
         <v>1978</v>
@@ -20634,7 +20649,7 @@
         <v>1979</v>
       </c>
       <c r="B1018" s="0" t="n">
-        <v>300170</v>
+        <v>355838</v>
       </c>
       <c r="C1018" s="0" t="s">
         <v>1980</v>
@@ -20648,7 +20663,7 @@
         <v>1981</v>
       </c>
       <c r="B1019" s="0" t="n">
-        <v>300121</v>
+        <v>300170</v>
       </c>
       <c r="C1019" s="0" t="s">
         <v>1982</v>
@@ -20662,7 +20677,7 @@
         <v>1983</v>
       </c>
       <c r="B1020" s="0" t="n">
-        <v>300440</v>
+        <v>300121</v>
       </c>
       <c r="C1020" s="0" t="s">
         <v>1984</v>
@@ -20676,7 +20691,7 @@
         <v>1985</v>
       </c>
       <c r="B1021" s="0" t="n">
-        <v>372010</v>
+        <v>300440</v>
       </c>
       <c r="C1021" s="0" t="s">
         <v>1986</v>
@@ -20690,7 +20705,7 @@
         <v>1987</v>
       </c>
       <c r="B1022" s="0" t="n">
-        <v>211010</v>
+        <v>372010</v>
       </c>
       <c r="C1022" s="0" t="s">
         <v>1988</v>
@@ -20701,27 +20716,27 @@
     </row>
     <row r="1023" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1023" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1023" s="0" t="s">
-        <v>4</v>
+        <v>1989</v>
+      </c>
+      <c r="B1023" s="0" t="n">
+        <v>211010</v>
       </c>
       <c r="C1023" s="0" t="s">
-        <v>4</v>
+        <v>1990</v>
       </c>
       <c r="D1023" s="0" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1024" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1024" s="0" t="s">
-        <v>1990</v>
-      </c>
-      <c r="B1024" s="0" t="n">
-        <v>358061</v>
+        <v>4</v>
+      </c>
+      <c r="B1024" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1024" s="0" t="s">
-        <v>1991</v>
+        <v>4</v>
       </c>
       <c r="D1024" s="0" t="s">
         <v>1991</v>
@@ -20732,7 +20747,7 @@
         <v>1992</v>
       </c>
       <c r="B1025" s="0" t="n">
-        <v>357120</v>
+        <v>358061</v>
       </c>
       <c r="C1025" s="0" t="s">
         <v>1993</v>
@@ -20746,7 +20761,7 @@
         <v>1994</v>
       </c>
       <c r="B1026" s="0" t="n">
-        <v>300083</v>
+        <v>357120</v>
       </c>
       <c r="C1026" s="0" t="s">
         <v>1995</v>
@@ -20760,7 +20775,7 @@
         <v>1996</v>
       </c>
       <c r="B1027" s="0" t="n">
-        <v>223050</v>
+        <v>300083</v>
       </c>
       <c r="C1027" s="0" t="s">
         <v>1997</v>
@@ -20774,7 +20789,7 @@
         <v>1998</v>
       </c>
       <c r="B1028" s="0" t="n">
-        <v>300059</v>
+        <v>223050</v>
       </c>
       <c r="C1028" s="0" t="s">
         <v>1999</v>
@@ -20788,24 +20803,24 @@
         <v>2000</v>
       </c>
       <c r="B1029" s="0" t="n">
-        <v>344140</v>
+        <v>300059</v>
       </c>
       <c r="C1029" s="0" t="s">
         <v>2001</v>
       </c>
       <c r="D1029" s="0" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1030" s="0" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B1030" s="0" t="n">
+        <v>344140</v>
+      </c>
+      <c r="C1030" s="0" t="s">
         <v>2003</v>
-      </c>
-      <c r="B1030" s="0" t="n">
-        <v>300720</v>
-      </c>
-      <c r="C1030" s="0" t="s">
-        <v>2004</v>
       </c>
       <c r="D1030" s="0" t="s">
         <v>2004</v>
@@ -20816,7 +20831,7 @@
         <v>2005</v>
       </c>
       <c r="B1031" s="0" t="n">
-        <v>211050</v>
+        <v>300720</v>
       </c>
       <c r="C1031" s="0" t="s">
         <v>2006</v>
@@ -20830,7 +20845,7 @@
         <v>2007</v>
       </c>
       <c r="B1032" s="0" t="n">
-        <v>211003</v>
+        <v>211050</v>
       </c>
       <c r="C1032" s="0" t="s">
         <v>2008</v>
@@ -20844,7 +20859,7 @@
         <v>2009</v>
       </c>
       <c r="B1033" s="0" t="n">
-        <v>300221</v>
+        <v>211003</v>
       </c>
       <c r="C1033" s="0" t="s">
         <v>2010</v>
@@ -20855,27 +20870,27 @@
     </row>
     <row r="1034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1034" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1034" s="0" t="s">
-        <v>4</v>
+        <v>2011</v>
+      </c>
+      <c r="B1034" s="0" t="n">
+        <v>300221</v>
       </c>
       <c r="C1034" s="0" t="s">
-        <v>4</v>
+        <v>2012</v>
       </c>
       <c r="D1034" s="0" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1035" s="0" t="s">
-        <v>2012</v>
-      </c>
-      <c r="B1035" s="0" t="n">
-        <v>264060</v>
+        <v>4</v>
+      </c>
+      <c r="B1035" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1035" s="0" t="s">
-        <v>2013</v>
+        <v>4</v>
       </c>
       <c r="D1035" s="0" t="s">
         <v>2013</v>
@@ -20886,7 +20901,7 @@
         <v>2014</v>
       </c>
       <c r="B1036" s="0" t="n">
-        <v>324030</v>
+        <v>264060</v>
       </c>
       <c r="C1036" s="0" t="s">
         <v>2015</v>
@@ -20897,27 +20912,27 @@
     </row>
     <row r="1037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1037" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1037" s="0" t="s">
-        <v>4</v>
+        <v>2016</v>
+      </c>
+      <c r="B1037" s="0" t="n">
+        <v>324030</v>
       </c>
       <c r="C1037" s="0" t="s">
-        <v>4</v>
+        <v>2017</v>
       </c>
       <c r="D1037" s="0" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1038" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1038" s="0" t="s">
-        <v>2017</v>
-      </c>
-      <c r="B1038" s="0" t="n">
-        <v>320150</v>
+        <v>4</v>
+      </c>
+      <c r="B1038" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1038" s="0" t="s">
-        <v>2018</v>
+        <v>4</v>
       </c>
       <c r="D1038" s="0" t="s">
         <v>2018</v>
@@ -20928,7 +20943,7 @@
         <v>2019</v>
       </c>
       <c r="B1039" s="0" t="n">
-        <v>321060</v>
+        <v>320150</v>
       </c>
       <c r="C1039" s="0" t="s">
         <v>2020</v>
@@ -20942,7 +20957,7 @@
         <v>2021</v>
       </c>
       <c r="B1040" s="0" t="n">
-        <v>311340</v>
+        <v>321060</v>
       </c>
       <c r="C1040" s="0" t="s">
         <v>2022</v>
@@ -20956,7 +20971,7 @@
         <v>2023</v>
       </c>
       <c r="B1041" s="0" t="n">
-        <v>210010</v>
+        <v>311340</v>
       </c>
       <c r="C1041" s="0" t="s">
         <v>2024</v>
@@ -20970,7 +20985,7 @@
         <v>2025</v>
       </c>
       <c r="B1042" s="0" t="n">
-        <v>241011</v>
+        <v>210010</v>
       </c>
       <c r="C1042" s="0" t="s">
         <v>2026</v>
@@ -20984,7 +20999,7 @@
         <v>2027</v>
       </c>
       <c r="B1043" s="0" t="n">
-        <v>241040</v>
+        <v>241011</v>
       </c>
       <c r="C1043" s="0" t="s">
         <v>2028</v>
@@ -20998,7 +21013,7 @@
         <v>2029</v>
       </c>
       <c r="B1044" s="0" t="n">
-        <v>263270</v>
+        <v>241040</v>
       </c>
       <c r="C1044" s="0" t="s">
         <v>2030</v>
@@ -21009,27 +21024,27 @@
     </row>
     <row r="1045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1045" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1045" s="0" t="s">
-        <v>4</v>
+        <v>2031</v>
+      </c>
+      <c r="B1045" s="0" t="n">
+        <v>263270</v>
       </c>
       <c r="C1045" s="0" t="s">
-        <v>4</v>
+        <v>2032</v>
       </c>
       <c r="D1045" s="0" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1046" s="0" t="s">
-        <v>2032</v>
-      </c>
-      <c r="B1046" s="0" t="n">
-        <v>353020</v>
+        <v>4</v>
+      </c>
+      <c r="B1046" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1046" s="0" t="s">
-        <v>2033</v>
+        <v>4</v>
       </c>
       <c r="D1046" s="0" t="s">
         <v>2033</v>
@@ -21037,27 +21052,27 @@
     </row>
     <row r="1047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1047" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1047" s="0" t="s">
-        <v>4</v>
+        <v>2034</v>
+      </c>
+      <c r="B1047" s="0" t="n">
+        <v>353020</v>
       </c>
       <c r="C1047" s="0" t="s">
-        <v>4</v>
+        <v>2035</v>
       </c>
       <c r="D1047" s="0" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1048" s="0" t="s">
-        <v>2035</v>
-      </c>
-      <c r="B1048" s="0" t="n">
-        <v>212051</v>
+        <v>4</v>
+      </c>
+      <c r="B1048" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1048" s="0" t="s">
-        <v>2036</v>
+        <v>4</v>
       </c>
       <c r="D1048" s="0" t="s">
         <v>2036</v>
@@ -21068,7 +21083,7 @@
         <v>2037</v>
       </c>
       <c r="B1049" s="0" t="n">
-        <v>221151</v>
+        <v>212051</v>
       </c>
       <c r="C1049" s="0" t="s">
         <v>2038</v>
@@ -21082,7 +21097,7 @@
         <v>2039</v>
       </c>
       <c r="B1050" s="0" t="n">
-        <v>312100</v>
+        <v>221151</v>
       </c>
       <c r="C1050" s="0" t="s">
         <v>2040</v>
@@ -21096,7 +21111,7 @@
         <v>2041</v>
       </c>
       <c r="B1051" s="0" t="n">
-        <v>358049</v>
+        <v>312100</v>
       </c>
       <c r="C1051" s="0" t="s">
         <v>2042</v>
@@ -21107,27 +21122,27 @@
     </row>
     <row r="1052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1052" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1052" s="0" t="s">
-        <v>4</v>
+        <v>2043</v>
+      </c>
+      <c r="B1052" s="0" t="n">
+        <v>358049</v>
       </c>
       <c r="C1052" s="0" t="s">
-        <v>4</v>
+        <v>2044</v>
       </c>
       <c r="D1052" s="0" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1053" s="0" t="s">
-        <v>2044</v>
-      </c>
-      <c r="B1053" s="0" t="n">
-        <v>358022</v>
+        <v>4</v>
+      </c>
+      <c r="B1053" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1053" s="0" t="s">
-        <v>2045</v>
+        <v>4</v>
       </c>
       <c r="D1053" s="0" t="s">
         <v>2045</v>
@@ -21138,7 +21153,7 @@
         <v>2046</v>
       </c>
       <c r="B1054" s="0" t="n">
-        <v>300021</v>
+        <v>358022</v>
       </c>
       <c r="C1054" s="0" t="s">
         <v>2047</v>
@@ -21152,7 +21167,7 @@
         <v>2048</v>
       </c>
       <c r="B1055" s="0" t="n">
-        <v>325010</v>
+        <v>300021</v>
       </c>
       <c r="C1055" s="0" t="s">
         <v>2049</v>
@@ -21163,16 +21178,16 @@
     </row>
     <row r="1056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1056" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1056" s="0" t="s">
-        <v>4</v>
+        <v>2050</v>
+      </c>
+      <c r="B1056" s="0" t="n">
+        <v>325010</v>
       </c>
       <c r="C1056" s="0" t="s">
-        <v>4</v>
+        <v>2051</v>
       </c>
       <c r="D1056" s="0" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21186,7 +21201,7 @@
         <v>4</v>
       </c>
       <c r="D1057" s="0" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21200,7 +21215,7 @@
         <v>4</v>
       </c>
       <c r="D1058" s="0" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21214,18 +21229,18 @@
         <v>4</v>
       </c>
       <c r="D1059" s="0" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1060" s="0" t="s">
-        <v>2054</v>
-      </c>
-      <c r="B1060" s="0" t="n">
-        <v>354050</v>
+        <v>4</v>
+      </c>
+      <c r="B1060" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1060" s="0" t="s">
-        <v>2055</v>
+        <v>4</v>
       </c>
       <c r="D1060" s="0" t="s">
         <v>2055</v>
@@ -21233,27 +21248,27 @@
     </row>
     <row r="1061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1061" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1061" s="0" t="s">
-        <v>4</v>
+        <v>2056</v>
+      </c>
+      <c r="B1061" s="0" t="n">
+        <v>354050</v>
       </c>
       <c r="C1061" s="0" t="s">
-        <v>4</v>
+        <v>2057</v>
       </c>
       <c r="D1061" s="0" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="1062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1062" s="0" t="s">
-        <v>2057</v>
-      </c>
-      <c r="B1062" s="0" t="n">
-        <v>311210</v>
+        <v>4</v>
+      </c>
+      <c r="B1062" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1062" s="0" t="s">
-        <v>2058</v>
+        <v>4</v>
       </c>
       <c r="D1062" s="0" t="s">
         <v>2058</v>
@@ -21261,27 +21276,27 @@
     </row>
     <row r="1063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1063" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1063" s="0" t="s">
-        <v>4</v>
+        <v>2059</v>
+      </c>
+      <c r="B1063" s="0" t="n">
+        <v>311210</v>
       </c>
       <c r="C1063" s="0" t="s">
-        <v>4</v>
+        <v>2060</v>
       </c>
       <c r="D1063" s="0" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1064" s="0" t="s">
-        <v>2060</v>
-      </c>
-      <c r="B1064" s="0" t="n">
-        <v>300480</v>
+        <v>4</v>
+      </c>
+      <c r="B1064" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C1064" s="0" t="s">
-        <v>2061</v>
+        <v>4</v>
       </c>
       <c r="D1064" s="0" t="s">
         <v>2061</v>
@@ -21292,7 +21307,7 @@
         <v>2062</v>
       </c>
       <c r="B1065" s="0" t="n">
-        <v>344111</v>
+        <v>300480</v>
       </c>
       <c r="C1065" s="0" t="s">
         <v>2063</v>
@@ -21306,7 +21321,7 @@
         <v>2064</v>
       </c>
       <c r="B1066" s="0" t="n">
-        <v>300124</v>
+        <v>344111</v>
       </c>
       <c r="C1066" s="0" t="s">
         <v>2065</v>
@@ -21320,7 +21335,7 @@
         <v>2066</v>
       </c>
       <c r="B1067" s="0" t="n">
-        <v>290180</v>
+        <v>300124</v>
       </c>
       <c r="C1067" s="0" t="s">
         <v>2067</v>
@@ -21334,7 +21349,7 @@
         <v>2068</v>
       </c>
       <c r="B1068" s="0" t="n">
-        <v>300040</v>
+        <v>290180</v>
       </c>
       <c r="C1068" s="0" t="s">
         <v>2069</v>
@@ -21348,7 +21363,7 @@
         <v>2070</v>
       </c>
       <c r="B1069" s="0" t="n">
-        <v>300120</v>
+        <v>300040</v>
       </c>
       <c r="C1069" s="0" t="s">
         <v>2071</v>
@@ -21362,7 +21377,7 @@
         <v>2072</v>
       </c>
       <c r="B1070" s="0" t="n">
-        <v>300242</v>
+        <v>300120</v>
       </c>
       <c r="C1070" s="0" t="s">
         <v>2073</v>
@@ -21376,24 +21391,24 @@
         <v>2074</v>
       </c>
       <c r="B1071" s="0" t="n">
-        <v>341061</v>
+        <v>300242</v>
       </c>
       <c r="C1071" s="0" t="s">
         <v>2075</v>
       </c>
       <c r="D1071" s="0" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="1072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1072" s="0" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B1072" s="0" t="n">
+        <v>341061</v>
+      </c>
+      <c r="C1072" s="0" t="s">
         <v>2077</v>
-      </c>
-      <c r="B1072" s="0" t="n">
-        <v>221021</v>
-      </c>
-      <c r="C1072" s="0" t="s">
-        <v>2078</v>
       </c>
       <c r="D1072" s="0" t="s">
         <v>2078</v>
@@ -21404,13 +21419,27 @@
         <v>2079</v>
       </c>
       <c r="B1073" s="0" t="n">
-        <v>327120</v>
+        <v>221021</v>
       </c>
       <c r="C1073" s="0" t="s">
         <v>2080</v>
       </c>
       <c r="D1073" s="0" t="s">
         <v>2080</v>
+      </c>
+    </row>
+    <row r="1074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1074" s="0" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B1074" s="0" t="n">
+        <v>327120</v>
+      </c>
+      <c r="C1074" s="0" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D1074" s="0" t="s">
+        <v>2082</v>
       </c>
     </row>
   </sheetData>
